--- a/Unity/Assets/Config/Excel/LongYinConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LongYinConfig.xlsx
@@ -37,7 +37,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="146">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>PreId</t>
+  </si>
+  <si>
+    <t>NeedKillBoss</t>
   </si>
   <si>
     <t>NeedUseNumber</t>
@@ -113,6 +116,9 @@
     <t>(array#sep=,),int</t>
   </si>
   <si>
+    <t>(array#sep=,),int#ref=MonsterConfigCategory</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -128,6 +134,9 @@
     <t>前置id</t>
   </si>
   <si>
+    <t>需要击杀Boss</t>
+  </si>
+  <si>
     <t>需要当前类型已使用天赋点</t>
   </si>
   <si>
@@ -141,6 +150,9 @@
   </si>
   <si>
     <t>焚心</t>
+  </si>
+  <si>
+    <t>310160</t>
   </si>
   <si>
     <t>RolePropertyAdd;100402;0.01#RolePropertyAdd;100402;0.02#RolePropertyAdd;100402;0.03</t>
@@ -171,6 +183,9 @@
   </si>
   <si>
     <t>RolePropertyAdd;223103;0.02#RolePropertyAdd;223103;0.04#RolePropertyAdd;223103;0.06#RolePropertyAdd;223103;0.08#RolePropertyAdd;223103;0.1</t>
+  </si>
+  <si>
+    <t>310161</t>
   </si>
   <si>
     <t>SkillIdAdd;1301002</t>
@@ -209,6 +224,9 @@
     <t>RolePropertyAdd;205603;0.1</t>
   </si>
   <si>
+    <t>310162</t>
+  </si>
+  <si>
     <t>RolePropertyAdd;203603;0.01#RolePropertyAdd;203603;0.02#RolePropertyAdd;203603;0.03#RolePropertyAdd;203603;0.04#RolePropertyAdd;203603;0.05</t>
   </si>
   <si>
@@ -236,6 +254,9 @@
     <t>13005</t>
   </si>
   <si>
+    <t>310163</t>
+  </si>
+  <si>
     <t>14001</t>
   </si>
   <si>
@@ -246,6 +267,9 @@
   </si>
   <si>
     <t>14005</t>
+  </si>
+  <si>
+    <t>310164</t>
   </si>
   <si>
     <t>15001</t>
@@ -11715,7 +11739,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{A2BF9778-1042-4617-A117-C7499CA77A48}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{EB20DA8A-F764-401E-8ADD-9572780B3F37}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -12015,7 +12039,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -12023,13 +12047,14 @@
     <col min="4" max="4" width="13.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.25" style="3" customWidth="1"/>
     <col min="6" max="6" width="29.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.375" customWidth="1"/>
-    <col min="9" max="9" width="108.25" customWidth="1"/>
-    <col min="10" max="10" width="43.75" customWidth="1"/>
+    <col min="7" max="7" width="38" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="108.25" customWidth="1"/>
+    <col min="11" max="11" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -12051,102 +12076,112 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>12</v>
+      <c r="J2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="3"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B5" s="3">
         <v>11001</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -12155,23 +12190,26 @@
         <v>1</v>
       </c>
       <c r="F5" s="9"/>
-      <c r="G5" s="3">
-        <v>1</v>
+      <c r="G5" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
         <v>10001</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="11" t="s">
-        <v>24</v>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B6" s="3">
         <v>11002</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -12182,23 +12220,24 @@
       <c r="F6" s="9">
         <v>11001</v>
       </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
+      <c r="G6" s="9"/>
       <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <v>10002</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11" t="s">
-        <v>25</v>
+      <c r="J6" s="12"/>
+      <c r="K6" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B7" s="3">
         <v>11003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -12209,21 +12248,22 @@
       <c r="F7" s="9">
         <v>11001</v>
       </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
+      <c r="G7" s="9"/>
       <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
         <v>10003</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="11"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B8" s="3">
         <v>11004</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -12232,25 +12272,26 @@
         <v>1</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G8" s="9"/>
       <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <v>10004</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11" t="s">
-        <v>27</v>
+      <c r="J8" s="12"/>
+      <c r="K8" s="11" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B9" s="3">
         <v>11005</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -12259,25 +12300,26 @@
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G9" s="9"/>
       <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
         <v>10005</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12" t="s">
-        <v>29</v>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B10" s="3">
         <v>11006</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -12286,25 +12328,26 @@
         <v>1</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G10" s="9"/>
       <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <v>10006</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11" t="s">
-        <v>31</v>
+      <c r="J10" s="12"/>
+      <c r="K10" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B11" s="3">
         <v>11007</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -12313,25 +12356,26 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G11" s="9"/>
       <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
         <v>10007</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11" t="s">
-        <v>32</v>
+      <c r="J11" s="12"/>
+      <c r="K11" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B12" s="3">
         <v>11008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -12340,25 +12384,26 @@
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G12" s="9"/>
       <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
         <v>10008</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11" t="s">
-        <v>33</v>
+      <c r="J12" s="12"/>
+      <c r="K12" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B13" s="3">
         <v>12001</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -12367,23 +12412,26 @@
         <v>1</v>
       </c>
       <c r="F13" s="9"/>
-      <c r="G13" s="3">
-        <v>1</v>
+      <c r="G13" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
         <v>10009</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11" t="s">
-        <v>34</v>
+      <c r="J13" s="12"/>
+      <c r="K13" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B14" s="3">
         <v>12002</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -12392,25 +12440,26 @@
         <v>1</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G14" s="9"/>
       <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
         <v>10010</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12" t="s">
-        <v>36</v>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B15" s="3">
         <v>12003</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -12419,25 +12468,26 @@
         <v>1</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G15" s="9"/>
       <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
         <v>10011</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="11" t="s">
-        <v>37</v>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B16" s="3">
         <v>12004</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -12446,25 +12496,26 @@
         <v>1</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G16" s="9"/>
       <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
         <v>10012</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11" t="s">
-        <v>39</v>
+      <c r="J16" s="12"/>
+      <c r="K16" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B17" s="3">
         <v>12005</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -12473,25 +12524,26 @@
         <v>1</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G17" s="9"/>
       <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
         <v>10013</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="11" t="s">
-        <v>41</v>
+      <c r="J17" s="12"/>
+      <c r="K17" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B18" s="3">
         <v>12006</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -12500,25 +12552,26 @@
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G18" s="9"/>
       <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
         <v>10014</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11" t="s">
-        <v>43</v>
+      <c r="J18" s="12"/>
+      <c r="K18" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B19" s="3">
         <v>12007</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -12527,25 +12580,26 @@
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="3">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G19" s="9"/>
       <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
         <v>10015</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12" t="s">
-        <v>44</v>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B20" s="3">
         <v>12008</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -12554,25 +12608,26 @@
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G20" s="9"/>
       <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
         <v>10016</v>
       </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11" t="s">
-        <v>45</v>
+      <c r="J20" s="12"/>
+      <c r="K20" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B21" s="3">
         <v>13001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -12581,23 +12636,26 @@
         <v>1</v>
       </c>
       <c r="F21" s="9"/>
-      <c r="G21" s="3">
-        <v>1</v>
+      <c r="G21" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
         <v>10017</v>
       </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="11" t="s">
-        <v>46</v>
+      <c r="J21" s="12"/>
+      <c r="K21" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B22" s="3">
         <v>13002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -12606,25 +12664,26 @@
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G22" s="9"/>
       <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
         <v>10018</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="11" t="s">
-        <v>48</v>
+      <c r="J22" s="12"/>
+      <c r="K22" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B23" s="3">
         <v>13003</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
@@ -12633,25 +12692,26 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G23" s="9"/>
       <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
         <v>10019</v>
       </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="11" t="s">
-        <v>49</v>
+      <c r="J23" s="12"/>
+      <c r="K23" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B24" s="3">
         <v>13004</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -12660,25 +12720,26 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="G24" s="9"/>
       <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
         <v>10020</v>
       </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="11" t="s">
-        <v>51</v>
+      <c r="J24" s="12"/>
+      <c r="K24" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B25" s="3">
         <v>13005</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -12687,25 +12748,26 @@
         <v>1</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G25" s="9"/>
       <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
         <v>10021</v>
       </c>
-      <c r="I25" s="12"/>
-      <c r="J25" s="11" t="s">
-        <v>53</v>
+      <c r="J25" s="12"/>
+      <c r="K25" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B26" s="3">
         <v>13006</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -12714,23 +12776,24 @@
         <v>1</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G26" s="9"/>
       <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
         <v>10001</v>
       </c>
-      <c r="I26" s="12"/>
-      <c r="J26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="11"/>
     </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B27" s="3">
         <v>13007</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
@@ -12739,23 +12802,24 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G27" s="9"/>
       <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
         <v>10002</v>
       </c>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="11"/>
     </row>
-    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B28" s="3">
         <v>13008</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -12764,23 +12828,24 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="3">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G28" s="9"/>
       <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
         <v>10003</v>
       </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="11"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="11"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B29" s="3">
         <v>14001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
@@ -12789,21 +12854,24 @@
         <v>1</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="3">
-        <v>1</v>
+      <c r="G29" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
         <v>10004</v>
       </c>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="11"/>
     </row>
-    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B30" s="3">
         <v>14002</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
@@ -12812,23 +12880,24 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G30" s="9"/>
       <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
         <v>10005</v>
       </c>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="11"/>
     </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B31" s="3">
         <v>14003</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
@@ -12837,23 +12906,24 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G31" s="9"/>
       <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
         <v>10006</v>
       </c>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="11"/>
     </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B32" s="3">
         <v>14004</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -12862,23 +12932,24 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G32" s="9"/>
       <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3">
         <v>10007</v>
       </c>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="11"/>
     </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B33" s="3">
         <v>14005</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -12887,23 +12958,24 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G33" s="9"/>
       <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
         <v>10008</v>
       </c>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="11"/>
     </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B34" s="3">
         <v>14006</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -12912,23 +12984,24 @@
         <v>1</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G34" s="9"/>
       <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
         <v>10009</v>
       </c>
-      <c r="I34" s="12"/>
-      <c r="J34" s="11"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="11"/>
     </row>
-    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B35" s="3">
         <v>14007</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -12937,23 +13010,24 @@
         <v>1</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G35" s="9"/>
       <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
         <v>10010</v>
       </c>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="11"/>
     </row>
-    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B36" s="3">
         <v>14008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -12962,23 +13036,24 @@
         <v>1</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36" s="3">
-        <v>1</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G36" s="9"/>
       <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
         <v>10011</v>
       </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="11"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="11"/>
     </row>
-    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B37" s="3">
         <v>15001</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -12987,21 +13062,24 @@
         <v>1</v>
       </c>
       <c r="F37" s="9"/>
-      <c r="G37" s="3">
-        <v>1</v>
+      <c r="G37" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3">
         <v>10012</v>
       </c>
-      <c r="I37" s="12"/>
-      <c r="J37" s="11"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="11"/>
     </row>
-    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B38" s="3">
         <v>15002</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -13010,23 +13088,24 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G38" s="9"/>
       <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3">
         <v>10013</v>
       </c>
-      <c r="I38" s="12"/>
-      <c r="J38" s="11"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="11"/>
     </row>
-    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B39" s="3">
         <v>15003</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -13035,23 +13114,24 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" s="3">
-        <v>1</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G39" s="9"/>
       <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3">
         <v>10014</v>
       </c>
-      <c r="I39" s="12"/>
-      <c r="J39" s="11"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="11"/>
     </row>
-    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B40" s="3">
         <v>15004</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
@@ -13060,23 +13140,24 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G40" s="9"/>
       <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3">
         <v>10015</v>
       </c>
-      <c r="I40" s="12"/>
-      <c r="J40" s="11"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="11"/>
     </row>
-    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B41" s="3">
         <v>15005</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
@@ -13085,23 +13166,24 @@
         <v>1</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G41" s="9"/>
       <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
         <v>10016</v>
       </c>
-      <c r="I41" s="12"/>
-      <c r="J41" s="11"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11"/>
     </row>
-    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B42" s="3">
         <v>15006</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -13110,23 +13192,24 @@
         <v>1</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42" s="3">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G42" s="9"/>
       <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
         <v>10017</v>
       </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="11"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="11"/>
     </row>
-    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B43" s="3">
         <v>15007</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D43" s="3">
         <v>1</v>
@@ -13135,23 +13218,24 @@
         <v>1</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G43" s="9"/>
       <c r="H43" s="3">
+        <v>1</v>
+      </c>
+      <c r="I43" s="3">
         <v>10018</v>
       </c>
-      <c r="I43" s="12"/>
-      <c r="J43" s="11"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="11"/>
     </row>
-    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B44" s="3">
         <v>15008</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -13160,23 +13244,24 @@
         <v>1</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G44" s="9"/>
       <c r="H44" s="3">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3">
         <v>10019</v>
       </c>
-      <c r="I44" s="12"/>
-      <c r="J44" s="11"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="11"/>
     </row>
-    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B45" s="3">
         <v>16001</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -13185,23 +13270,24 @@
         <v>1</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="G45" s="9"/>
       <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3">
         <v>10020</v>
       </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="11"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="11"/>
     </row>
-    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B46" s="3">
         <v>16002</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -13210,23 +13296,24 @@
         <v>1</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G46" s="9"/>
       <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="I46" s="3">
         <v>10021</v>
       </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="11"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="11"/>
     </row>
-    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B47" s="3">
         <v>16003</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -13235,23 +13322,24 @@
         <v>1</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G47" s="9"/>
       <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" s="3">
         <v>10021</v>
       </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="11"/>
     </row>
-    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B48" s="3">
         <v>16004</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -13260,23 +13348,24 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G48" s="9"/>
       <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" s="3">
         <v>10021</v>
       </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="11"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="11"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B49" s="3">
         <v>16005</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -13285,39 +13374,41 @@
         <v>1</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G49" s="9"/>
       <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" s="3">
         <v>10021</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="11"/>
     </row>
-    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A50" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="3"/>
+      <c r="G50" s="9"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="11"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="11"/>
     </row>
-    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B51" s="3">
         <v>21001</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
@@ -13326,25 +13417,28 @@
         <v>1</v>
       </c>
       <c r="F51" s="9"/>
-      <c r="G51" s="3">
-        <v>1</v>
+      <c r="G51" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" s="3">
         <v>10001</v>
       </c>
-      <c r="I51" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>24</v>
+      <c r="J51" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B52" s="3">
         <v>21002</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D52" s="3">
         <v>2</v>
@@ -13353,27 +13447,28 @@
         <v>1</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G52" s="9"/>
       <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3">
         <v>10002</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>72</v>
+      <c r="J52" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B53" s="3">
         <v>21003</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D53" s="3">
         <v>2</v>
@@ -13382,27 +13477,28 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G53" s="3">
-        <v>1</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G53" s="9"/>
       <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
         <v>10003</v>
       </c>
-      <c r="I53" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>74</v>
+      <c r="J53" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B54" s="3">
         <v>21004</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D54" s="3">
         <v>2</v>
@@ -13411,27 +13507,28 @@
         <v>1</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G54" s="9"/>
       <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3">
         <v>10004</v>
       </c>
-      <c r="I54" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>77</v>
+      <c r="J54" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B55" s="3">
         <v>21005</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D55" s="3">
         <v>2</v>
@@ -13440,27 +13537,28 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G55" s="3">
-        <v>1</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G55" s="9"/>
       <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
         <v>10005</v>
       </c>
-      <c r="I55" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>80</v>
+      <c r="J55" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B56" s="3">
         <v>21006</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D56" s="3">
         <v>2</v>
@@ -13469,27 +13567,28 @@
         <v>1</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G56" s="3">
-        <v>1</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G56" s="9"/>
       <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3">
         <v>10006</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>83</v>
+      <c r="J56" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B57" s="3">
         <v>21007</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -13498,27 +13597,28 @@
         <v>1</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G57" s="9"/>
       <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" s="3">
         <v>10007</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>85</v>
+      <c r="J57" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B58" s="3">
         <v>21008</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D58" s="3">
         <v>2</v>
@@ -13527,27 +13627,28 @@
         <v>1</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G58" s="9"/>
       <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" s="3">
         <v>10008</v>
       </c>
-      <c r="I58" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>87</v>
+      <c r="J58" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B59" s="3">
         <v>22001</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D59" s="3">
         <v>2</v>
@@ -13556,25 +13657,26 @@
         <v>1</v>
       </c>
       <c r="F59" s="9"/>
-      <c r="G59" s="3">
-        <v>1</v>
-      </c>
+      <c r="G59" s="9"/>
       <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" s="3">
         <v>10009</v>
       </c>
-      <c r="I59" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>89</v>
+      <c r="J59" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B60" s="3">
         <v>22002</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D60" s="3">
         <v>2</v>
@@ -13583,27 +13685,28 @@
         <v>1</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G60" s="9"/>
       <c r="H60" s="3">
+        <v>1</v>
+      </c>
+      <c r="I60" s="3">
         <v>10010</v>
       </c>
-      <c r="I60" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>92</v>
+      <c r="J60" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B61" s="3">
         <v>22003</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D61" s="3">
         <v>2</v>
@@ -13612,27 +13715,28 @@
         <v>1</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G61" s="9"/>
       <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3">
         <v>10011</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>94</v>
+      <c r="J61" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B62" s="3">
         <v>22004</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D62" s="3">
         <v>2</v>
@@ -13641,27 +13745,28 @@
         <v>1</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G62" s="9"/>
       <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" s="3">
         <v>10012</v>
       </c>
-      <c r="I62" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>97</v>
+      <c r="J62" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B63" s="3">
         <v>22005</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
@@ -13670,27 +13775,28 @@
         <v>1</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G63" s="3">
-        <v>1</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G63" s="9"/>
       <c r="H63" s="3">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3">
         <v>10013</v>
       </c>
-      <c r="I63" s="12" t="s">
-        <v>99</v>
-      </c>
       <c r="J63" s="12" t="s">
-        <v>44</v>
+        <v>107</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B64" s="3">
         <v>22006</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D64" s="3">
         <v>2</v>
@@ -13699,27 +13805,28 @@
         <v>1</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G64" s="3">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G64" s="9"/>
       <c r="H64" s="3">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3">
         <v>10014</v>
       </c>
-      <c r="I64" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>102</v>
+      <c r="J64" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B65" s="3">
         <v>22007</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D65" s="3">
         <v>2</v>
@@ -13728,27 +13835,28 @@
         <v>1</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G65" s="3">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G65" s="9"/>
       <c r="H65" s="3">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3">
         <v>10015</v>
       </c>
-      <c r="I65" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>104</v>
+      <c r="J65" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B66" s="3">
         <v>22008</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D66" s="3">
         <v>2</v>
@@ -13757,27 +13865,28 @@
         <v>1</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G66" s="9"/>
       <c r="H66" s="3">
+        <v>1</v>
+      </c>
+      <c r="I66" s="3">
         <v>10016</v>
       </c>
-      <c r="I66" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>106</v>
+      <c r="J66" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B67" s="3">
         <v>23001</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D67" s="3">
         <v>2</v>
@@ -13786,25 +13895,28 @@
         <v>1</v>
       </c>
       <c r="F67" s="9"/>
-      <c r="G67" s="3">
-        <v>1</v>
+      <c r="G67" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="I67" s="3">
         <v>10017</v>
       </c>
-      <c r="I67" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>33</v>
+      <c r="J67" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B68" s="3">
         <v>23002</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D68" s="3">
         <v>2</v>
@@ -13813,27 +13925,28 @@
         <v>1</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G68" s="3">
-        <v>1</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G68" s="9"/>
       <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3">
         <v>10018</v>
       </c>
-      <c r="I68" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>110</v>
+      <c r="J68" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B69" s="3">
         <v>23003</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -13842,27 +13955,28 @@
         <v>1</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G69" s="3">
-        <v>1</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G69" s="9"/>
       <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3">
         <v>10019</v>
       </c>
-      <c r="I69" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>112</v>
+      <c r="J69" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B70" s="3">
         <v>23004</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D70" s="3">
         <v>2</v>
@@ -13871,27 +13985,28 @@
         <v>1</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="G70" s="9"/>
       <c r="H70" s="3">
+        <v>1</v>
+      </c>
+      <c r="I70" s="3">
         <v>10020</v>
       </c>
-      <c r="I70" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>115</v>
+      <c r="J70" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B71" s="3">
         <v>23005</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D71" s="3">
         <v>2</v>
@@ -13900,27 +14015,28 @@
         <v>1</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G71" s="3">
-        <v>1</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="G71" s="9"/>
       <c r="H71" s="3">
+        <v>1</v>
+      </c>
+      <c r="I71" s="3">
         <v>10021</v>
       </c>
-      <c r="I71" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>118</v>
+      <c r="J71" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B72" s="3">
         <v>23006</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -13929,25 +14045,26 @@
         <v>1</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G72" s="9"/>
       <c r="H72" s="3">
+        <v>1</v>
+      </c>
+      <c r="I72" s="3">
         <v>10001</v>
       </c>
-      <c r="I72" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J72" s="11"/>
+      <c r="J72" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K72" s="11"/>
     </row>
-    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B73" s="3">
         <v>23007</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D73" s="3">
         <v>2</v>
@@ -13956,25 +14073,26 @@
         <v>1</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G73" s="3">
-        <v>1</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G73" s="9"/>
       <c r="H73" s="3">
+        <v>1</v>
+      </c>
+      <c r="I73" s="3">
         <v>10002</v>
       </c>
-      <c r="I73" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J73" s="11"/>
+      <c r="J73" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K73" s="11"/>
     </row>
-    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B74" s="3">
         <v>23008</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
@@ -13983,25 +14101,26 @@
         <v>1</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G74" s="3">
-        <v>1</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G74" s="9"/>
       <c r="H74" s="3">
+        <v>1</v>
+      </c>
+      <c r="I74" s="3">
         <v>10003</v>
       </c>
-      <c r="I74" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J74" s="11"/>
+      <c r="J74" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K74" s="11"/>
     </row>
-    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B75" s="3">
         <v>24001</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -14010,23 +14129,26 @@
         <v>1</v>
       </c>
       <c r="F75" s="9"/>
-      <c r="G75" s="3">
-        <v>1</v>
+      <c r="G75" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="H75" s="3">
+        <v>1</v>
+      </c>
+      <c r="I75" s="3">
         <v>10004</v>
       </c>
-      <c r="I75" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="J75" s="11"/>
+      <c r="J75" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="K75" s="11"/>
     </row>
-    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B76" s="3">
         <v>24002</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D76" s="3">
         <v>2</v>
@@ -14035,25 +14157,26 @@
         <v>1</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G76" s="9"/>
       <c r="H76" s="3">
+        <v>1</v>
+      </c>
+      <c r="I76" s="3">
         <v>10005</v>
       </c>
-      <c r="I76" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J76" s="11"/>
+      <c r="J76" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K76" s="11"/>
     </row>
-    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B77" s="3">
         <v>24003</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D77" s="3">
         <v>2</v>
@@ -14062,25 +14185,26 @@
         <v>1</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G77" s="3">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G77" s="9"/>
       <c r="H77" s="3">
+        <v>1</v>
+      </c>
+      <c r="I77" s="3">
         <v>10006</v>
       </c>
-      <c r="I77" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="J77" s="11"/>
+      <c r="J77" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K77" s="11"/>
     </row>
-    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B78" s="3">
         <v>24004</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D78" s="3">
         <v>2</v>
@@ -14089,25 +14213,26 @@
         <v>1</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="G78" s="3">
-        <v>1</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G78" s="9"/>
       <c r="H78" s="3">
+        <v>1</v>
+      </c>
+      <c r="I78" s="3">
         <v>10007</v>
       </c>
-      <c r="I78" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J78" s="11"/>
+      <c r="J78" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K78" s="11"/>
     </row>
-    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B79" s="3">
         <v>24005</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
@@ -14116,25 +14241,26 @@
         <v>1</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G79" s="3">
-        <v>1</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G79" s="9"/>
       <c r="H79" s="3">
+        <v>1</v>
+      </c>
+      <c r="I79" s="3">
         <v>10008</v>
       </c>
-      <c r="I79" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J79" s="11"/>
+      <c r="J79" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K79" s="11"/>
     </row>
-    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B80" s="3">
         <v>24006</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -14143,25 +14269,26 @@
         <v>1</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G80" s="3">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="G80" s="9"/>
       <c r="H80" s="3">
+        <v>1</v>
+      </c>
+      <c r="I80" s="3">
         <v>10009</v>
       </c>
-      <c r="I80" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J80" s="11"/>
+      <c r="J80" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K80" s="11"/>
     </row>
-    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B81" s="3">
         <v>24007</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -14170,25 +14297,26 @@
         <v>1</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="G81" s="9"/>
       <c r="H81" s="3">
+        <v>1</v>
+      </c>
+      <c r="I81" s="3">
         <v>10010</v>
       </c>
-      <c r="I81" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="J81" s="11"/>
+      <c r="J81" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="K81" s="11"/>
     </row>
-    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B82" s="3">
         <v>24008</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D82" s="3">
         <v>2</v>
@@ -14197,25 +14325,26 @@
         <v>1</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G82" s="3">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="G82" s="9"/>
       <c r="H82" s="3">
+        <v>1</v>
+      </c>
+      <c r="I82" s="3">
         <v>10011</v>
       </c>
-      <c r="I82" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J82" s="11"/>
+      <c r="J82" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="K82" s="11"/>
     </row>
-    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B83" s="3">
         <v>25001</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D83" s="3">
         <v>2</v>
@@ -14224,23 +14353,26 @@
         <v>1</v>
       </c>
       <c r="F83" s="9"/>
-      <c r="G83" s="3">
-        <v>1</v>
+      <c r="G83" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="H83" s="3">
+        <v>1</v>
+      </c>
+      <c r="I83" s="3">
         <v>10012</v>
       </c>
-      <c r="I83" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J83" s="11"/>
+      <c r="J83" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K83" s="11"/>
     </row>
-    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B84" s="3">
         <v>25002</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D84" s="3">
         <v>2</v>
@@ -14249,25 +14381,26 @@
         <v>1</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G84" s="3">
-        <v>1</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G84" s="9"/>
       <c r="H84" s="3">
+        <v>1</v>
+      </c>
+      <c r="I84" s="3">
         <v>10013</v>
       </c>
-      <c r="I84" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J84" s="11"/>
+      <c r="J84" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="K84" s="11"/>
     </row>
-    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B85" s="3">
         <v>25003</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D85" s="3">
         <v>2</v>
@@ -14276,25 +14409,26 @@
         <v>1</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G85" s="3">
-        <v>1</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G85" s="9"/>
       <c r="H85" s="3">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3">
         <v>10014</v>
       </c>
-      <c r="I85" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="J85" s="11"/>
+      <c r="J85" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="K85" s="11"/>
     </row>
-    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B86" s="3">
         <v>25004</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D86" s="3">
         <v>2</v>
@@ -14303,25 +14437,26 @@
         <v>1</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G86" s="3">
-        <v>1</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="G86" s="9"/>
       <c r="H86" s="3">
+        <v>1</v>
+      </c>
+      <c r="I86" s="3">
         <v>10015</v>
       </c>
-      <c r="I86" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="J86" s="11"/>
+      <c r="J86" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="K86" s="11"/>
     </row>
-    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B87" s="3">
         <v>25005</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -14330,25 +14465,26 @@
         <v>1</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G87" s="3">
-        <v>1</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="G87" s="9"/>
       <c r="H87" s="3">
+        <v>1</v>
+      </c>
+      <c r="I87" s="3">
         <v>10016</v>
       </c>
-      <c r="I87" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J87" s="11"/>
+      <c r="J87" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K87" s="11"/>
     </row>
-    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B88" s="3">
         <v>25006</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -14357,25 +14493,26 @@
         <v>1</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G88" s="3">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G88" s="9"/>
       <c r="H88" s="3">
+        <v>1</v>
+      </c>
+      <c r="I88" s="3">
         <v>10017</v>
       </c>
-      <c r="I88" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="J88" s="11"/>
+      <c r="J88" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="K88" s="11"/>
     </row>
-    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B89" s="3">
         <v>25007</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D89" s="3">
         <v>2</v>
@@ -14384,25 +14521,26 @@
         <v>1</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G89" s="9"/>
       <c r="H89" s="3">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3">
         <v>10018</v>
       </c>
-      <c r="I89" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J89" s="11"/>
+      <c r="J89" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="K89" s="11"/>
     </row>
-    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B90" s="3">
         <v>25008</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D90" s="3">
         <v>2</v>
@@ -14411,25 +14549,26 @@
         <v>1</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G90" s="3">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G90" s="9"/>
       <c r="H90" s="3">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3">
         <v>10019</v>
       </c>
-      <c r="I90" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J90" s="11"/>
+      <c r="J90" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K90" s="11"/>
     </row>
-    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B91" s="3">
         <v>26001</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D91" s="3">
         <v>2</v>
@@ -14438,25 +14577,26 @@
         <v>1</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G91" s="3">
-        <v>1</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G91" s="9"/>
       <c r="H91" s="3">
+        <v>1</v>
+      </c>
+      <c r="I91" s="3">
         <v>10020</v>
       </c>
-      <c r="I91" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J91" s="11"/>
+      <c r="J91" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="K91" s="11"/>
     </row>
-    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B92" s="3">
         <v>26002</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D92" s="3">
         <v>2</v>
@@ -14465,25 +14605,26 @@
         <v>1</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G92" s="3">
-        <v>1</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G92" s="9"/>
       <c r="H92" s="3">
+        <v>1</v>
+      </c>
+      <c r="I92" s="3">
         <v>10021</v>
       </c>
-      <c r="I92" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J92" s="11"/>
+      <c r="J92" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K92" s="11"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:11">
       <c r="B93" s="3">
         <v>26003</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -14492,21 +14633,22 @@
         <v>1</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G93" s="3">
-        <v>1</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G93" s="9"/>
       <c r="H93" s="3">
+        <v>1</v>
+      </c>
+      <c r="I93" s="3">
         <v>10021</v>
       </c>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:11">
       <c r="B94" s="3">
         <v>26004</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D94" s="3">
         <v>2</v>
@@ -14515,21 +14657,22 @@
         <v>1</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G94" s="3">
-        <v>1</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="G94" s="9"/>
       <c r="H94" s="3">
+        <v>1</v>
+      </c>
+      <c r="I94" s="3">
         <v>10021</v>
       </c>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:11">
       <c r="B95" s="3">
         <v>26005</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D95" s="3">
         <v>2</v>
@@ -14538,12 +14681,13 @@
         <v>1</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="G95" s="3">
-        <v>1</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G95" s="9"/>
       <c r="H95" s="3">
+        <v>1</v>
+      </c>
+      <c r="I95" s="3">
         <v>10021</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/LongYinConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LongYinConfig.xlsx
@@ -37,7 +37,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="144">
   <si>
     <t>##var</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>NeedKillBoss</t>
-  </si>
-  <si>
-    <t>NeedUseNumber</t>
   </si>
   <si>
     <t>Icon</t>
@@ -135,9 +132,6 @@
   </si>
   <si>
     <t>需要击杀Boss</t>
-  </si>
-  <si>
-    <t>需要当前类型已使用天赋点</t>
   </si>
   <si>
     <t>描述</t>
@@ -12039,7 +12033,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -12048,13 +12042,12 @@
     <col min="5" max="5" width="12.25" style="3" customWidth="1"/>
     <col min="6" max="6" width="29.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="38" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.375" customWidth="1"/>
-    <col min="10" max="10" width="108.25" customWidth="1"/>
-    <col min="11" max="11" width="43.75" customWidth="1"/>
+    <col min="8" max="8" width="11.375" customWidth="1"/>
+    <col min="9" max="9" width="108.25" customWidth="1"/>
+    <col min="10" max="10" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -12076,95 +12069,86 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>12</v>
+      <c r="H2" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>13</v>
+      <c r="J2" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="8" t="s">
+    </row>
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -12172,16 +12156,15 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="11"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B5" s="3">
         <v>11001</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -12191,25 +12174,22 @@
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
         <v>10001</v>
       </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="11" t="s">
-        <v>28</v>
+      <c r="I5" s="12"/>
+      <c r="J5" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B6" s="3">
         <v>11002</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -12222,22 +12202,19 @@
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
         <v>10002</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="11" t="s">
-        <v>29</v>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B7" s="3">
         <v>11003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -12250,20 +12227,17 @@
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3">
         <v>10003</v>
       </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B8" s="3">
         <v>11004</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -12272,54 +12246,48 @@
         <v>1</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3">
         <v>10004</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="11" t="s">
-        <v>31</v>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B9" s="3">
         <v>11005</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3">
         <v>10005</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12" t="s">
-        <v>33</v>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B10" s="3">
         <v>11006</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -12328,26 +12296,23 @@
         <v>1</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="3">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3">
         <v>10006</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="11" t="s">
-        <v>35</v>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B11" s="3">
         <v>11007</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -12356,26 +12321,23 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3">
         <v>10007</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="11" t="s">
-        <v>36</v>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B12" s="3">
         <v>11008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -12384,26 +12346,23 @@
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="3">
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
         <v>10008</v>
       </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="11" t="s">
-        <v>37</v>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B13" s="3">
         <v>12001</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -12413,25 +12372,22 @@
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
         <v>10009</v>
       </c>
-      <c r="J13" s="12"/>
-      <c r="K13" s="11" t="s">
-        <v>39</v>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B14" s="3">
         <v>12002</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -12440,26 +12396,23 @@
         <v>1</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="3">
-        <v>1</v>
-      </c>
-      <c r="I14" s="3">
         <v>10010</v>
       </c>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12" t="s">
-        <v>41</v>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B15" s="3">
         <v>12003</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -12468,26 +12421,23 @@
         <v>1</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="3">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3">
         <v>10011</v>
       </c>
-      <c r="J15" s="12"/>
-      <c r="K15" s="11" t="s">
-        <v>42</v>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B16" s="3">
         <v>12004</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -12496,54 +12446,48 @@
         <v>1</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="3">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3">
         <v>10012</v>
       </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="11" t="s">
-        <v>44</v>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B17" s="3">
         <v>12005</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="3">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3">
         <v>10013</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="11" t="s">
-        <v>46</v>
+      <c r="I17" s="12"/>
+      <c r="J17" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B18" s="3">
         <v>12006</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -12552,26 +12496,23 @@
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="3">
-        <v>1</v>
-      </c>
-      <c r="I18" s="3">
         <v>10014</v>
       </c>
-      <c r="J18" s="12"/>
-      <c r="K18" s="11" t="s">
-        <v>48</v>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B19" s="3">
         <v>12007</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -12580,26 +12521,23 @@
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="3">
-        <v>1</v>
-      </c>
-      <c r="I19" s="3">
         <v>10015</v>
       </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12" t="s">
-        <v>49</v>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B20" s="3">
         <v>12008</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -12608,26 +12546,23 @@
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="3">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3">
         <v>10016</v>
       </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="11" t="s">
-        <v>50</v>
+      <c r="I20" s="12"/>
+      <c r="J20" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B21" s="3">
         <v>13001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -12637,25 +12572,22 @@
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H21" s="3">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3">
         <v>10017</v>
       </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="11" t="s">
-        <v>52</v>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B22" s="3">
         <v>13002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -12664,26 +12596,23 @@
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3">
         <v>10018</v>
       </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="11" t="s">
-        <v>54</v>
+      <c r="I22" s="12"/>
+      <c r="J22" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B23" s="3">
         <v>13003</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
@@ -12692,26 +12621,23 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="3">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3">
         <v>10019</v>
       </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="11" t="s">
-        <v>55</v>
+      <c r="I23" s="12"/>
+      <c r="J23" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B24" s="3">
         <v>13004</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -12720,54 +12646,48 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3">
         <v>10020</v>
       </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="11" t="s">
-        <v>57</v>
+      <c r="I24" s="12"/>
+      <c r="J24" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B25" s="3">
         <v>13005</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
       </c>
       <c r="E25" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3">
         <v>10021</v>
       </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="11" t="s">
-        <v>59</v>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B26" s="3">
         <v>13006</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -12776,24 +12696,21 @@
         <v>1</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="3">
-        <v>1</v>
-      </c>
-      <c r="I26" s="3">
         <v>10001</v>
       </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="11"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="11"/>
     </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B27" s="3">
         <v>13007</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
@@ -12802,24 +12719,21 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="3">
-        <v>1</v>
-      </c>
-      <c r="I27" s="3">
         <v>10002</v>
       </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
     </row>
-    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B28" s="3">
         <v>13008</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -12828,24 +12742,21 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="3">
         <v>10003</v>
       </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="11"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="11"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B29" s="3">
         <v>14001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
@@ -12855,23 +12766,20 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H29" s="3">
-        <v>1</v>
-      </c>
-      <c r="I29" s="3">
         <v>10004</v>
       </c>
-      <c r="J29" s="12"/>
-      <c r="K29" s="11"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="11"/>
     </row>
-    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B30" s="3">
         <v>14002</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
@@ -12880,24 +12788,21 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="3">
-        <v>1</v>
-      </c>
-      <c r="I30" s="3">
         <v>10005</v>
       </c>
-      <c r="J30" s="12"/>
-      <c r="K30" s="11"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="11"/>
     </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B31" s="3">
         <v>14003</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
@@ -12906,24 +12811,21 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="3">
-        <v>1</v>
-      </c>
-      <c r="I31" s="3">
         <v>10006</v>
       </c>
-      <c r="J31" s="12"/>
-      <c r="K31" s="11"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="11"/>
     </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B32" s="3">
         <v>14004</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -12932,50 +12834,44 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="3">
-        <v>1</v>
-      </c>
-      <c r="I32" s="3">
         <v>10007</v>
       </c>
-      <c r="J32" s="12"/>
-      <c r="K32" s="11"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="11"/>
     </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B33" s="3">
         <v>14005</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
       </c>
       <c r="E33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="3">
-        <v>1</v>
-      </c>
-      <c r="I33" s="3">
         <v>10008</v>
       </c>
-      <c r="J33" s="12"/>
-      <c r="K33" s="11"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="11"/>
     </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B34" s="3">
         <v>14006</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -12984,24 +12880,21 @@
         <v>1</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" s="3">
         <v>10009</v>
       </c>
-      <c r="J34" s="12"/>
-      <c r="K34" s="11"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="11"/>
     </row>
-    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B35" s="3">
         <v>14007</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -13010,24 +12903,21 @@
         <v>1</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" s="3">
         <v>10010</v>
       </c>
-      <c r="J35" s="12"/>
-      <c r="K35" s="11"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="11"/>
     </row>
-    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B36" s="3">
         <v>14008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -13036,24 +12926,21 @@
         <v>1</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="3">
-        <v>1</v>
-      </c>
-      <c r="I36" s="3">
         <v>10011</v>
       </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="11"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="11"/>
     </row>
-    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B37" s="3">
         <v>15001</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -13063,23 +12950,20 @@
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H37" s="3">
-        <v>1</v>
-      </c>
-      <c r="I37" s="3">
         <v>10012</v>
       </c>
-      <c r="J37" s="12"/>
-      <c r="K37" s="11"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="11"/>
     </row>
-    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B38" s="3">
         <v>15002</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -13088,24 +12972,21 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" s="3">
         <v>10013</v>
       </c>
-      <c r="J38" s="12"/>
-      <c r="K38" s="11"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="11"/>
     </row>
-    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B39" s="3">
         <v>15003</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -13114,24 +12995,21 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="3">
-        <v>1</v>
-      </c>
-      <c r="I39" s="3">
         <v>10014</v>
       </c>
-      <c r="J39" s="12"/>
-      <c r="K39" s="11"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="11"/>
     </row>
-    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B40" s="3">
         <v>15004</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
@@ -13140,50 +13018,44 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="3">
-        <v>1</v>
-      </c>
-      <c r="I40" s="3">
         <v>10015</v>
       </c>
-      <c r="J40" s="12"/>
-      <c r="K40" s="11"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="11"/>
     </row>
-    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B41" s="3">
         <v>15005</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
       </c>
       <c r="E41" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" s="3">
         <v>10016</v>
       </c>
-      <c r="J41" s="12"/>
-      <c r="K41" s="11"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="11"/>
     </row>
-    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B42" s="3">
         <v>15006</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -13192,24 +13064,21 @@
         <v>1</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G42" s="9"/>
       <c r="H42" s="3">
-        <v>1</v>
-      </c>
-      <c r="I42" s="3">
         <v>10017</v>
       </c>
-      <c r="J42" s="12"/>
-      <c r="K42" s="11"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="11"/>
     </row>
-    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B43" s="3">
         <v>15007</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D43" s="3">
         <v>1</v>
@@ -13218,24 +13087,21 @@
         <v>1</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G43" s="9"/>
       <c r="H43" s="3">
-        <v>1</v>
-      </c>
-      <c r="I43" s="3">
         <v>10018</v>
       </c>
-      <c r="J43" s="12"/>
-      <c r="K43" s="11"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="11"/>
     </row>
-    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B44" s="3">
         <v>15008</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -13244,24 +13110,21 @@
         <v>1</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="3">
-        <v>1</v>
-      </c>
-      <c r="I44" s="3">
         <v>10019</v>
       </c>
-      <c r="J44" s="12"/>
-      <c r="K44" s="11"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="11"/>
     </row>
-    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B45" s="3">
         <v>16001</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -13270,24 +13133,21 @@
         <v>1</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="3">
-        <v>1</v>
-      </c>
-      <c r="I45" s="3">
         <v>10020</v>
       </c>
-      <c r="J45" s="12"/>
-      <c r="K45" s="11"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="11"/>
     </row>
-    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B46" s="3">
         <v>16002</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -13296,24 +13156,21 @@
         <v>1</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="3">
-        <v>1</v>
-      </c>
-      <c r="I46" s="3">
         <v>10021</v>
       </c>
-      <c r="J46" s="12"/>
-      <c r="K46" s="11"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="11"/>
     </row>
-    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B47" s="3">
         <v>16003</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -13322,24 +13179,21 @@
         <v>1</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G47" s="9"/>
       <c r="H47" s="3">
-        <v>1</v>
-      </c>
-      <c r="I47" s="3">
         <v>10021</v>
       </c>
-      <c r="J47" s="10"/>
-      <c r="K47" s="11"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="11"/>
     </row>
-    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B48" s="3">
         <v>16004</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -13348,24 +13202,21 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G48" s="9"/>
       <c r="H48" s="3">
-        <v>1</v>
-      </c>
-      <c r="I48" s="3">
         <v>10021</v>
       </c>
-      <c r="J48" s="10"/>
-      <c r="K48" s="11"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="11"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B49" s="3">
         <v>16005</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -13374,24 +13225,21 @@
         <v>1</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="3">
-        <v>1</v>
-      </c>
-      <c r="I49" s="3">
         <v>10021</v>
       </c>
-      <c r="J49" s="10"/>
-      <c r="K49" s="11"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="11"/>
     </row>
-    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -13399,16 +13247,15 @@
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="11"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="11"/>
     </row>
-    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B51" s="3">
         <v>21001</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
@@ -13418,27 +13265,24 @@
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H51" s="3">
-        <v>1</v>
-      </c>
-      <c r="I51" s="3">
         <v>10001</v>
       </c>
-      <c r="J51" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>28</v>
+      <c r="I51" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B52" s="3">
         <v>21002</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D52" s="3">
         <v>2</v>
@@ -13447,28 +13291,25 @@
         <v>1</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G52" s="9"/>
       <c r="H52" s="3">
-        <v>1</v>
-      </c>
-      <c r="I52" s="3">
         <v>10002</v>
       </c>
-      <c r="J52" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>80</v>
+      <c r="I52" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B53" s="3">
         <v>21003</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D53" s="3">
         <v>2</v>
@@ -13477,28 +13318,25 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="3">
-        <v>1</v>
-      </c>
-      <c r="I53" s="3">
         <v>10003</v>
       </c>
-      <c r="J53" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>82</v>
+      <c r="I53" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B54" s="3">
         <v>21004</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D54" s="3">
         <v>2</v>
@@ -13507,58 +13345,52 @@
         <v>1</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="3">
-        <v>1</v>
-      </c>
-      <c r="I54" s="3">
         <v>10004</v>
       </c>
-      <c r="J54" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>85</v>
+      <c r="I54" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B55" s="3">
         <v>21005</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D55" s="3">
         <v>2</v>
       </c>
       <c r="E55" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="3">
-        <v>1</v>
-      </c>
-      <c r="I55" s="3">
         <v>10005</v>
       </c>
-      <c r="J55" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>88</v>
+      <c r="I55" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B56" s="3">
         <v>21006</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D56" s="3">
         <v>2</v>
@@ -13567,28 +13399,25 @@
         <v>1</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G56" s="9"/>
       <c r="H56" s="3">
-        <v>1</v>
-      </c>
-      <c r="I56" s="3">
         <v>10006</v>
       </c>
-      <c r="J56" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>91</v>
+      <c r="I56" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B57" s="3">
         <v>21007</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -13597,28 +13426,25 @@
         <v>1</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="3">
-        <v>1</v>
-      </c>
-      <c r="I57" s="3">
         <v>10007</v>
       </c>
-      <c r="J57" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>93</v>
+      <c r="I57" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B58" s="3">
         <v>21008</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D58" s="3">
         <v>2</v>
@@ -13627,28 +13453,25 @@
         <v>1</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="3">
-        <v>1</v>
-      </c>
-      <c r="I58" s="3">
         <v>10008</v>
       </c>
-      <c r="J58" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>95</v>
+      <c r="I58" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B59" s="3">
         <v>22001</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D59" s="3">
         <v>2</v>
@@ -13659,24 +13482,21 @@
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="3">
-        <v>1</v>
-      </c>
-      <c r="I59" s="3">
         <v>10009</v>
       </c>
-      <c r="J59" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>97</v>
+      <c r="I59" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B60" s="3">
         <v>22002</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D60" s="3">
         <v>2</v>
@@ -13685,28 +13505,25 @@
         <v>1</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="3">
-        <v>1</v>
-      </c>
-      <c r="I60" s="3">
         <v>10010</v>
       </c>
-      <c r="J60" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>100</v>
+      <c r="I60" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B61" s="3">
         <v>22003</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D61" s="3">
         <v>2</v>
@@ -13715,28 +13532,25 @@
         <v>1</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="3">
-        <v>1</v>
-      </c>
-      <c r="I61" s="3">
         <v>10011</v>
       </c>
-      <c r="J61" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>102</v>
+      <c r="I61" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B62" s="3">
         <v>22004</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D62" s="3">
         <v>2</v>
@@ -13745,58 +13559,52 @@
         <v>1</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="3">
-        <v>1</v>
-      </c>
-      <c r="I62" s="3">
         <v>10012</v>
       </c>
-      <c r="J62" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="K62" s="11" t="s">
-        <v>105</v>
+      <c r="I62" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B63" s="3">
         <v>22005</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
       </c>
       <c r="E63" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="3">
-        <v>1</v>
-      </c>
-      <c r="I63" s="3">
         <v>10013</v>
       </c>
+      <c r="I63" s="12" t="s">
+        <v>105</v>
+      </c>
       <c r="J63" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K63" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="B64" s="3">
         <v>22006</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D64" s="3">
         <v>2</v>
@@ -13805,28 +13613,25 @@
         <v>1</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="3">
-        <v>1</v>
-      </c>
-      <c r="I64" s="3">
         <v>10014</v>
       </c>
-      <c r="J64" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="K64" s="11" t="s">
-        <v>110</v>
+      <c r="I64" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B65" s="3">
         <v>22007</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D65" s="3">
         <v>2</v>
@@ -13835,28 +13640,25 @@
         <v>1</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G65" s="9"/>
       <c r="H65" s="3">
-        <v>1</v>
-      </c>
-      <c r="I65" s="3">
         <v>10015</v>
       </c>
-      <c r="J65" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="K65" s="11" t="s">
-        <v>112</v>
+      <c r="I65" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B66" s="3">
         <v>22008</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D66" s="3">
         <v>2</v>
@@ -13865,28 +13667,25 @@
         <v>1</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G66" s="9"/>
       <c r="H66" s="3">
-        <v>1</v>
-      </c>
-      <c r="I66" s="3">
         <v>10016</v>
       </c>
-      <c r="J66" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K66" s="11" t="s">
-        <v>114</v>
+      <c r="I66" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B67" s="3">
         <v>23001</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D67" s="3">
         <v>2</v>
@@ -13896,27 +13695,24 @@
       </c>
       <c r="F67" s="9"/>
       <c r="G67" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H67" s="3">
-        <v>1</v>
-      </c>
-      <c r="I67" s="3">
         <v>10017</v>
       </c>
-      <c r="J67" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="K67" s="11" t="s">
-        <v>37</v>
+      <c r="I67" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B68" s="3">
         <v>23002</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D68" s="3">
         <v>2</v>
@@ -13925,28 +13721,25 @@
         <v>1</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G68" s="9"/>
       <c r="H68" s="3">
-        <v>1</v>
-      </c>
-      <c r="I68" s="3">
         <v>10018</v>
       </c>
-      <c r="J68" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="K68" s="11" t="s">
-        <v>118</v>
+      <c r="I68" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B69" s="3">
         <v>23003</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -13955,28 +13748,25 @@
         <v>1</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G69" s="9"/>
       <c r="H69" s="3">
-        <v>1</v>
-      </c>
-      <c r="I69" s="3">
         <v>10019</v>
       </c>
-      <c r="J69" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K69" s="11" t="s">
-        <v>120</v>
+      <c r="I69" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B70" s="3">
         <v>23004</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D70" s="3">
         <v>2</v>
@@ -13985,58 +13775,52 @@
         <v>1</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G70" s="9"/>
       <c r="H70" s="3">
-        <v>1</v>
-      </c>
-      <c r="I70" s="3">
         <v>10020</v>
       </c>
-      <c r="J70" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="K70" s="11" t="s">
-        <v>123</v>
+      <c r="I70" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B71" s="3">
         <v>23005</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D71" s="3">
         <v>2</v>
       </c>
       <c r="E71" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G71" s="9"/>
       <c r="H71" s="3">
-        <v>1</v>
-      </c>
-      <c r="I71" s="3">
         <v>10021</v>
       </c>
-      <c r="J71" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="K71" s="11" t="s">
-        <v>126</v>
+      <c r="I71" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B72" s="3">
         <v>23006</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -14045,26 +13829,23 @@
         <v>1</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G72" s="9"/>
       <c r="H72" s="3">
-        <v>1</v>
-      </c>
-      <c r="I72" s="3">
         <v>10001</v>
       </c>
-      <c r="J72" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="K72" s="11"/>
+      <c r="I72" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J72" s="11"/>
     </row>
-    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B73" s="3">
         <v>23007</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D73" s="3">
         <v>2</v>
@@ -14073,26 +13854,23 @@
         <v>1</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G73" s="9"/>
       <c r="H73" s="3">
-        <v>1</v>
-      </c>
-      <c r="I73" s="3">
         <v>10002</v>
       </c>
-      <c r="J73" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K73" s="11"/>
+      <c r="I73" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J73" s="11"/>
     </row>
-    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B74" s="3">
         <v>23008</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
@@ -14101,26 +13879,23 @@
         <v>1</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G74" s="9"/>
       <c r="H74" s="3">
-        <v>1</v>
-      </c>
-      <c r="I74" s="3">
         <v>10003</v>
       </c>
-      <c r="J74" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="K74" s="11"/>
+      <c r="I74" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J74" s="11"/>
     </row>
-    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B75" s="3">
         <v>24001</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -14130,25 +13905,22 @@
       </c>
       <c r="F75" s="9"/>
       <c r="G75" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H75" s="3">
-        <v>1</v>
-      </c>
-      <c r="I75" s="3">
         <v>10004</v>
       </c>
-      <c r="J75" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K75" s="11"/>
+      <c r="I75" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J75" s="11"/>
     </row>
-    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B76" s="3">
         <v>24002</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D76" s="3">
         <v>2</v>
@@ -14157,26 +13929,23 @@
         <v>1</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G76" s="9"/>
       <c r="H76" s="3">
-        <v>1</v>
-      </c>
-      <c r="I76" s="3">
         <v>10005</v>
       </c>
-      <c r="J76" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K76" s="11"/>
+      <c r="I76" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J76" s="11"/>
     </row>
-    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B77" s="3">
         <v>24003</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D77" s="3">
         <v>2</v>
@@ -14185,26 +13954,23 @@
         <v>1</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="3">
-        <v>1</v>
-      </c>
-      <c r="I77" s="3">
         <v>10006</v>
       </c>
-      <c r="J77" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="K77" s="11"/>
+      <c r="I77" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="J77" s="11"/>
     </row>
-    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B78" s="3">
         <v>24004</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D78" s="3">
         <v>2</v>
@@ -14213,54 +13979,48 @@
         <v>1</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="3">
-        <v>1</v>
-      </c>
-      <c r="I78" s="3">
         <v>10007</v>
       </c>
-      <c r="J78" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="K78" s="11"/>
+      <c r="I78" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="J78" s="11"/>
     </row>
-    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B79" s="3">
         <v>24005</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
       </c>
       <c r="E79" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G79" s="9"/>
       <c r="H79" s="3">
-        <v>1</v>
-      </c>
-      <c r="I79" s="3">
         <v>10008</v>
       </c>
-      <c r="J79" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K79" s="11"/>
+      <c r="I79" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J79" s="11"/>
     </row>
-    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B80" s="3">
         <v>24006</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -14269,26 +14029,23 @@
         <v>1</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G80" s="9"/>
       <c r="H80" s="3">
-        <v>1</v>
-      </c>
-      <c r="I80" s="3">
         <v>10009</v>
       </c>
-      <c r="J80" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K80" s="11"/>
+      <c r="I80" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J80" s="11"/>
     </row>
-    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B81" s="3">
         <v>24007</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -14297,26 +14054,23 @@
         <v>1</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G81" s="9"/>
       <c r="H81" s="3">
-        <v>1</v>
-      </c>
-      <c r="I81" s="3">
         <v>10010</v>
       </c>
-      <c r="J81" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="K81" s="11"/>
+      <c r="I81" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81" s="11"/>
     </row>
-    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B82" s="3">
         <v>24008</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D82" s="3">
         <v>2</v>
@@ -14325,26 +14079,23 @@
         <v>1</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="3">
-        <v>1</v>
-      </c>
-      <c r="I82" s="3">
         <v>10011</v>
       </c>
-      <c r="J82" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="K82" s="11"/>
+      <c r="I82" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J82" s="11"/>
     </row>
-    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B83" s="3">
         <v>25001</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D83" s="3">
         <v>2</v>
@@ -14354,25 +14105,22 @@
       </c>
       <c r="F83" s="9"/>
       <c r="G83" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H83" s="3">
-        <v>1</v>
-      </c>
-      <c r="I83" s="3">
         <v>10012</v>
       </c>
-      <c r="J83" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="K83" s="11"/>
+      <c r="I83" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J83" s="11"/>
     </row>
-    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B84" s="3">
         <v>25002</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D84" s="3">
         <v>2</v>
@@ -14381,26 +14129,23 @@
         <v>1</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G84" s="9"/>
       <c r="H84" s="3">
-        <v>1</v>
-      </c>
-      <c r="I84" s="3">
         <v>10013</v>
       </c>
-      <c r="J84" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K84" s="11"/>
+      <c r="I84" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J84" s="11"/>
     </row>
-    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B85" s="3">
         <v>25003</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D85" s="3">
         <v>2</v>
@@ -14409,26 +14154,23 @@
         <v>1</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G85" s="9"/>
       <c r="H85" s="3">
-        <v>1</v>
-      </c>
-      <c r="I85" s="3">
         <v>10014</v>
       </c>
-      <c r="J85" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="K85" s="11"/>
+      <c r="I85" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="J85" s="11"/>
     </row>
-    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B86" s="3">
         <v>25004</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D86" s="3">
         <v>2</v>
@@ -14437,54 +14179,48 @@
         <v>1</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G86" s="9"/>
       <c r="H86" s="3">
-        <v>1</v>
-      </c>
-      <c r="I86" s="3">
         <v>10015</v>
       </c>
-      <c r="J86" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="K86" s="11"/>
+      <c r="I86" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="J86" s="11"/>
     </row>
-    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B87" s="3">
         <v>25005</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
       </c>
       <c r="E87" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G87" s="9"/>
       <c r="H87" s="3">
-        <v>1</v>
-      </c>
-      <c r="I87" s="3">
         <v>10016</v>
       </c>
-      <c r="J87" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K87" s="11"/>
+      <c r="I87" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J87" s="11"/>
     </row>
-    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B88" s="3">
         <v>25006</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -14493,26 +14229,23 @@
         <v>1</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G88" s="9"/>
       <c r="H88" s="3">
-        <v>1</v>
-      </c>
-      <c r="I88" s="3">
         <v>10017</v>
       </c>
-      <c r="J88" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="K88" s="11"/>
+      <c r="I88" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J88" s="11"/>
     </row>
-    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B89" s="3">
         <v>25007</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D89" s="3">
         <v>2</v>
@@ -14521,26 +14254,23 @@
         <v>1</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G89" s="9"/>
       <c r="H89" s="3">
-        <v>1</v>
-      </c>
-      <c r="I89" s="3">
         <v>10018</v>
       </c>
-      <c r="J89" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="K89" s="11"/>
+      <c r="I89" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="J89" s="11"/>
     </row>
-    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B90" s="3">
         <v>25008</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D90" s="3">
         <v>2</v>
@@ -14549,26 +14279,23 @@
         <v>1</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="3">
-        <v>1</v>
-      </c>
-      <c r="I90" s="3">
         <v>10019</v>
       </c>
-      <c r="J90" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K90" s="11"/>
+      <c r="I90" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J90" s="11"/>
     </row>
-    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B91" s="3">
         <v>26001</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D91" s="3">
         <v>2</v>
@@ -14577,26 +14304,23 @@
         <v>1</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="3">
-        <v>1</v>
-      </c>
-      <c r="I91" s="3">
         <v>10020</v>
       </c>
-      <c r="J91" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="K91" s="11"/>
+      <c r="I91" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="J91" s="11"/>
     </row>
-    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
       <c r="B92" s="3">
         <v>26002</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D92" s="3">
         <v>2</v>
@@ -14605,26 +14329,23 @@
         <v>1</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G92" s="9"/>
       <c r="H92" s="3">
-        <v>1</v>
-      </c>
-      <c r="I92" s="3">
         <v>10021</v>
       </c>
-      <c r="J92" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="K92" s="11"/>
+      <c r="I92" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J92" s="11"/>
     </row>
-    <row r="93" spans="2:11">
+    <row r="93" spans="2:10">
       <c r="B93" s="3">
         <v>26003</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -14633,22 +14354,19 @@
         <v>1</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="3">
-        <v>1</v>
-      </c>
-      <c r="I93" s="3">
         <v>10021</v>
       </c>
     </row>
-    <row r="94" spans="2:11">
+    <row r="94" spans="2:10">
       <c r="B94" s="3">
         <v>26004</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D94" s="3">
         <v>2</v>
@@ -14657,22 +14375,19 @@
         <v>1</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G94" s="9"/>
       <c r="H94" s="3">
-        <v>1</v>
-      </c>
-      <c r="I94" s="3">
         <v>10021</v>
       </c>
     </row>
-    <row r="95" spans="2:11">
+    <row r="95" spans="2:10">
       <c r="B95" s="3">
         <v>26005</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D95" s="3">
         <v>2</v>
@@ -14681,13 +14396,10 @@
         <v>1</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G95" s="9"/>
       <c r="H95" s="3">
-        <v>1</v>
-      </c>
-      <c r="I95" s="3">
         <v>10021</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/LongYinConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LongYinConfig.xlsx
@@ -37,7 +37,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -86,6 +86,9 @@
     <t>Lv</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>PreId</t>
   </si>
   <si>
@@ -110,12 +113,21 @@
     <t>string</t>
   </si>
   <si>
+    <t>LongYinType</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
     <t>(array#sep=,),int#ref=MonsterConfigCategory</t>
   </si>
   <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -128,6 +140,9 @@
     <t>等级</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>前置id</t>
   </si>
   <si>
@@ -149,6 +164,9 @@
     <t>310160</t>
   </si>
   <si>
+    <t>描述。。。。</t>
+  </si>
+  <si>
     <t>RolePropertyAdd;100402;0.01#RolePropertyAdd;100402;0.02#RolePropertyAdd;100402;0.03</t>
   </si>
   <si>
@@ -291,6 +309,24 @@
   </si>
   <si>
     <t>15004,11004</t>
+  </si>
+  <si>
+    <t>双龙觉醒</t>
+  </si>
+  <si>
+    <t>双龙觉醒很牛逼</t>
+  </si>
+  <si>
+    <t>三龙觉醒</t>
+  </si>
+  <si>
+    <t>三龙觉醒很牛逼</t>
+  </si>
+  <si>
+    <t>五龙觉醒</t>
+  </si>
+  <si>
+    <t>五龙觉醒很牛逼</t>
   </si>
   <si>
     <t>法师</t>
@@ -9017,7 +9053,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -9051,9 +9087,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2476" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11733,7 +11766,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{EB20DA8A-F764-401E-8ADD-9572780B3F37}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{5A70E253-88C2-49D2-983F-EC4F1DC39A57}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -12033,21 +12066,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="34.5" customWidth="1"/>
-    <col min="4" max="4" width="13.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="29.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="38" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.375" customWidth="1"/>
-    <col min="9" max="9" width="108.25" customWidth="1"/>
-    <col min="10" max="10" width="43.75" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="4" max="4" width="7.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="62.875" customWidth="1"/>
+    <col min="11" max="11" width="58.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -12069,1328 +12103,1546 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>12</v>
+      <c r="J2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="F4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B5" s="3">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B6" s="3">
         <v>11001</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
         <v>10001</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="11" t="s">
-        <v>26</v>
+      <c r="J6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B6" s="3">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B7" s="3">
         <v>11002</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9">
         <v>11001</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="3">
+      <c r="H7" s="9"/>
+      <c r="I7" s="3">
         <v>10002</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11" t="s">
-        <v>27</v>
+      <c r="J7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B7" s="3">
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B8" s="3">
         <v>11003</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9">
         <v>11001</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="3">
+      <c r="H8" s="9"/>
+      <c r="I8" s="3">
         <v>10003</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
+      <c r="J8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="11"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B8" s="3">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B9" s="3">
         <v>11004</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="3">
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="3">
         <v>10004</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B9" s="3">
-        <v>11005</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="3">
-        <v>10005</v>
-      </c>
-      <c r="I9" s="12"/>
       <c r="J9" s="12" t="s">
         <v>31</v>
       </c>
+      <c r="K9" s="11" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B10" s="3">
+        <v>11005</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="3">
+        <v>10005</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B11" s="3">
         <v>11006</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="3">
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="3">
         <v>10006</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11" t="s">
-        <v>33</v>
+      <c r="J11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B11" s="3">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B12" s="3">
         <v>11007</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="3">
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="3">
         <v>10007</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11" t="s">
-        <v>34</v>
+      <c r="J12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B12" s="3">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B13" s="3">
         <v>11008</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="3">
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="3">
         <v>10008</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11" t="s">
-        <v>35</v>
+      <c r="J13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B13" s="3">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B14" s="3">
         <v>12001</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="3">
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="3">
         <v>10009</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11" t="s">
-        <v>37</v>
+      <c r="J14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B14" s="3">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B15" s="3">
         <v>12002</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="3">
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="3">
         <v>10010</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12" t="s">
-        <v>39</v>
+      <c r="J15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B15" s="3">
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B16" s="3">
         <v>12003</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="3">
+      <c r="C16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="3">
         <v>10011</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="11" t="s">
-        <v>40</v>
+      <c r="J16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B16" s="3">
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B17" s="3">
         <v>12004</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="3">
+      <c r="C17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="3">
         <v>10012</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11" t="s">
-        <v>42</v>
+      <c r="J17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B17" s="3">
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B18" s="3">
         <v>12005</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
         <v>3</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="3">
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="3">
         <v>10013</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="11" t="s">
-        <v>44</v>
+      <c r="J18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B18" s="3">
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B19" s="3">
         <v>12006</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="3">
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="3">
         <v>10014</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11" t="s">
-        <v>46</v>
+      <c r="J19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B19" s="3">
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B20" s="3">
         <v>12007</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="3">
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="3">
         <v>10015</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12" t="s">
-        <v>47</v>
+      <c r="J20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B20" s="3">
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B21" s="3">
         <v>12008</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="3">
+      <c r="C21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="3">
         <v>10016</v>
       </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11" t="s">
-        <v>48</v>
+      <c r="J21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B21" s="3">
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B22" s="3">
         <v>13001</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="3">
         <v>10017</v>
       </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="11" t="s">
-        <v>50</v>
+      <c r="J22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B22" s="3">
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B23" s="3">
         <v>13002</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="3">
+      <c r="C23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="3">
         <v>10018</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="11" t="s">
-        <v>52</v>
+      <c r="J23" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B23" s="3">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B24" s="3">
         <v>13003</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="3">
+      <c r="C24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="3">
         <v>10019</v>
       </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="11" t="s">
-        <v>53</v>
+      <c r="J24" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B24" s="3">
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B25" s="3">
         <v>13004</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="3">
+      <c r="C25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3">
+        <v>3</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="3">
         <v>10020</v>
       </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="11" t="s">
-        <v>55</v>
+      <c r="J25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B25" s="3">
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B26" s="3">
         <v>13005</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="3">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
         <v>3</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="3">
+      <c r="F26" s="3">
+        <v>3</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="3">
         <v>10021</v>
       </c>
-      <c r="I25" s="12"/>
-      <c r="J25" s="11" t="s">
-        <v>57</v>
+      <c r="J26" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B26" s="3">
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B27" s="3">
         <v>13006</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="3">
+      <c r="C27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="3">
         <v>10001</v>
       </c>
-      <c r="I26" s="12"/>
-      <c r="J26" s="11"/>
+      <c r="J27" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="11"/>
     </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B27" s="3">
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B28" s="3">
         <v>13007</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="3">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="3">
+      <c r="C28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="3">
         <v>10002</v>
       </c>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
+      <c r="J28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="11"/>
     </row>
-    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B28" s="3">
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B29" s="3">
         <v>13008</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>1</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="3">
+      <c r="C29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="3">
         <v>10003</v>
       </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="11"/>
+      <c r="J29" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="11"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B29" s="3">
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B30" s="3">
         <v>14001</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3">
-        <v>1</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="C30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="3">
         <v>10004</v>
       </c>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
+      <c r="J30" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" s="11"/>
     </row>
-    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B30" s="3">
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B31" s="3">
         <v>14002</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
-        <v>1</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="3">
+      <c r="C31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>4</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="3">
         <v>10005</v>
       </c>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
+      <c r="J31" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="11"/>
     </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B31" s="3">
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B32" s="3">
         <v>14003</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3">
-        <v>1</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="3">
+      <c r="C32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>4</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="3">
         <v>10006</v>
       </c>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
+      <c r="J32" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="11"/>
     </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B32" s="3">
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B33" s="3">
         <v>14004</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="3">
+      <c r="C33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="3">
         <v>10007</v>
       </c>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
+      <c r="J33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="11"/>
     </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B33" s="3">
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B34" s="3">
         <v>14005</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="3">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="C34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
         <v>3</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="3">
+      <c r="F34" s="3">
+        <v>4</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" s="9"/>
+      <c r="I34" s="3">
         <v>10008</v>
       </c>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
+      <c r="J34" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="11"/>
     </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B34" s="3">
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B35" s="3">
         <v>14006</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3">
-        <v>1</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="3">
+      <c r="C35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3">
+        <v>4</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="3">
         <v>10009</v>
       </c>
-      <c r="I34" s="12"/>
-      <c r="J34" s="11"/>
+      <c r="J35" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="11"/>
     </row>
-    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B35" s="3">
+    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B36" s="3">
         <v>14007</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="3">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3">
-        <v>1</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="3">
+      <c r="C36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3">
+        <v>4</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" s="9"/>
+      <c r="I36" s="3">
         <v>10010</v>
       </c>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
+      <c r="J36" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" s="11"/>
     </row>
-    <row r="36" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B36" s="3">
+    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B37" s="3">
         <v>14008</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3">
-        <v>1</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="3">
+      <c r="C37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <v>4</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" s="9"/>
+      <c r="I37" s="3">
         <v>10011</v>
       </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="11"/>
+      <c r="J37" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" s="11"/>
     </row>
-    <row r="37" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B37" s="3">
+    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B38" s="3">
         <v>15001</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="3">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3">
-        <v>1</v>
-      </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="3">
+      <c r="C38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <v>5</v>
+      </c>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" s="3">
         <v>10012</v>
       </c>
-      <c r="I37" s="12"/>
-      <c r="J37" s="11"/>
+      <c r="J38" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="11"/>
     </row>
-    <row r="38" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B38" s="3">
+    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B39" s="3">
         <v>15002</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3">
-        <v>1</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="3">
+      <c r="C39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3">
+        <v>5</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39" s="9"/>
+      <c r="I39" s="3">
         <v>10013</v>
       </c>
-      <c r="I38" s="12"/>
-      <c r="J38" s="11"/>
+      <c r="J39" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="11"/>
     </row>
-    <row r="39" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B39" s="3">
+    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B40" s="3">
         <v>15003</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="3">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3">
-        <v>1</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="3">
+      <c r="C40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="3">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3">
+        <v>5</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="9"/>
+      <c r="I40" s="3">
         <v>10014</v>
       </c>
-      <c r="I39" s="12"/>
-      <c r="J39" s="11"/>
+      <c r="J40" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="11"/>
     </row>
-    <row r="40" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B40" s="3">
+    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B41" s="3">
         <v>15004</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="3">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3">
-        <v>1</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="3">
+      <c r="C41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3">
+        <v>5</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" s="9"/>
+      <c r="I41" s="3">
         <v>10015</v>
       </c>
-      <c r="I40" s="12"/>
-      <c r="J40" s="11"/>
+      <c r="J41" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" s="11"/>
     </row>
-    <row r="41" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B41" s="3">
+    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B42" s="3">
         <v>15005</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="3">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="C42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3">
         <v>3</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="9"/>
-      <c r="H41" s="3">
+      <c r="F42" s="3">
+        <v>5</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="9"/>
+      <c r="I42" s="3">
         <v>10016</v>
       </c>
-      <c r="I41" s="12"/>
-      <c r="J41" s="11"/>
+      <c r="J42" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" s="11"/>
     </row>
-    <row r="42" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B42" s="3">
+    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B43" s="3">
         <v>15006</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3">
-        <v>1</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="3">
+      <c r="C43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3">
+        <v>5</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="9"/>
+      <c r="I43" s="3">
         <v>10017</v>
       </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="11"/>
+      <c r="J43" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="11"/>
     </row>
-    <row r="43" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B43" s="3">
+    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B44" s="3">
         <v>15007</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="3">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="3">
+      <c r="C44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="3">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3">
+        <v>5</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H44" s="9"/>
+      <c r="I44" s="3">
         <v>10018</v>
       </c>
-      <c r="I43" s="12"/>
-      <c r="J43" s="11"/>
+      <c r="J44" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="11"/>
     </row>
-    <row r="44" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B44" s="3">
+    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B45" s="3">
         <v>15008</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="3">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="3">
+      <c r="C45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3">
+        <v>5</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45" s="9"/>
+      <c r="I45" s="3">
         <v>10019</v>
       </c>
-      <c r="I44" s="12"/>
-      <c r="J44" s="11"/>
+      <c r="J45" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="11"/>
     </row>
-    <row r="45" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B45" s="3">
+    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B46" s="3">
         <v>16001</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="3">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="3">
+      <c r="C46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H46" s="9"/>
+      <c r="I46" s="3">
         <v>10020</v>
       </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="11"/>
+      <c r="J46" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="11"/>
     </row>
-    <row r="46" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B46" s="3">
+    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B47" s="3">
         <v>16002</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3">
-        <v>1</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="3">
+      <c r="C47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H47" s="9"/>
+      <c r="I47" s="3">
         <v>10021</v>
       </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="11"/>
+      <c r="J47" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" s="11"/>
     </row>
-    <row r="47" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B47" s="3">
+    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B48" s="3">
         <v>16003</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="3">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G47" s="9"/>
-      <c r="H47" s="3">
+      <c r="C48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" s="9"/>
+      <c r="I48" s="3">
         <v>10021</v>
       </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="J48" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48" s="11"/>
     </row>
-    <row r="48" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
-      <c r="B48" s="3">
+    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B49" s="3">
         <v>16004</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="3">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G48" s="9"/>
-      <c r="H48" s="3">
+      <c r="C49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" s="9"/>
+      <c r="I49" s="3">
         <v>10021</v>
       </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="11"/>
+      <c r="J49" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="11"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B49" s="3">
+    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B50" s="3">
         <v>16005</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="3">
-        <v>1</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G49" s="9"/>
-      <c r="H49" s="3">
+      <c r="C50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1</v>
+      </c>
+      <c r="E50" s="3">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H50" s="9"/>
+      <c r="I50" s="3">
         <v>10021</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="J50" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" s="11"/>
     </row>
-    <row r="50" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="A50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="11"/>
+    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B51" s="3">
+        <v>17001</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>6</v>
+      </c>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K51" s="11"/>
     </row>
-    <row r="51" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B51" s="3">
+    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B52" s="3">
+        <v>17002</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3">
+        <v>7</v>
+      </c>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K52" s="11"/>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B53" s="3">
+        <v>17003</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3">
+        <v>8</v>
+      </c>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K53" s="11"/>
+    </row>
+    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A54" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="11"/>
+    </row>
+    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="B55" s="3">
         <v>21001</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="3">
-        <v>2</v>
-      </c>
-      <c r="E51" s="3">
-        <v>1</v>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H51" s="3">
-        <v>10001</v>
-      </c>
-      <c r="I51" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B52" s="3">
-        <v>21002</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="3">
-        <v>2</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G52" s="9"/>
-      <c r="H52" s="3">
-        <v>10002</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B53" s="3">
-        <v>21003</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="3">
-        <v>2</v>
-      </c>
-      <c r="E53" s="3">
-        <v>1</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="3">
-        <v>10003</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B54" s="3">
-        <v>21004</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="3">
-        <v>2</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="3">
-        <v>10004</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
-      <c r="B55" s="3">
-        <v>21005</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D55" s="3">
         <v>2</v>
       </c>
       <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="F55" s="3">
+        <v>1</v>
       </c>
       <c r="G55" s="9"/>
-      <c r="H55" s="3">
-        <v>10005</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>86</v>
+      <c r="H55" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3">
+        <v>10001</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B56" s="3">
-        <v>21006</v>
+        <v>21002</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D56" s="3">
         <v>2</v>
@@ -13398,26 +13650,29 @@
       <c r="E56" s="3">
         <v>1</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="3">
-        <v>10006</v>
-      </c>
-      <c r="I56" s="12" t="s">
+      <c r="F56" s="3">
+        <v>1</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="H56" s="9"/>
+      <c r="I56" s="3">
+        <v>10002</v>
+      </c>
+      <c r="J56" s="12" t="s">
         <v>89</v>
       </c>
+      <c r="K56" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B57" s="3">
-        <v>21007</v>
+        <v>21003</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -13425,26 +13680,29 @@
       <c r="E57" s="3">
         <v>1</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G57" s="9"/>
-      <c r="H57" s="3">
-        <v>10007</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="J57" s="11" t="s">
+      <c r="F57" s="3">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" s="9"/>
+      <c r="I57" s="3">
+        <v>10003</v>
+      </c>
+      <c r="J57" s="12" t="s">
         <v>91</v>
       </c>
+      <c r="K57" s="11" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B58" s="3">
-        <v>21008</v>
+        <v>21004</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D58" s="3">
         <v>2</v>
@@ -13452,51 +13710,59 @@
       <c r="E58" s="3">
         <v>1</v>
       </c>
-      <c r="F58" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="3">
-        <v>10008</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J58" s="11" t="s">
+      <c r="F58" s="3">
+        <v>1</v>
+      </c>
+      <c r="G58" s="9" t="s">
         <v>93</v>
       </c>
+      <c r="H58" s="9"/>
+      <c r="I58" s="3">
+        <v>10004</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>95</v>
+      </c>
     </row>
-    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B59" s="3">
-        <v>22001</v>
+        <v>21005</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D59" s="3">
         <v>2</v>
       </c>
       <c r="E59" s="3">
-        <v>1</v>
-      </c>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="3">
-        <v>10009</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>95</v>
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H59" s="9"/>
+      <c r="I59" s="3">
+        <v>10005</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B60" s="3">
-        <v>22002</v>
+        <v>21006</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D60" s="3">
         <v>2</v>
@@ -13504,26 +13770,29 @@
       <c r="E60" s="3">
         <v>1</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G60" s="9"/>
-      <c r="H60" s="3">
-        <v>10010</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>98</v>
+      <c r="F60" s="3">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H60" s="9"/>
+      <c r="I60" s="3">
+        <v>10006</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B61" s="3">
-        <v>22003</v>
+        <v>21007</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D61" s="3">
         <v>2</v>
@@ -13531,26 +13800,29 @@
       <c r="E61" s="3">
         <v>1</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G61" s="9"/>
-      <c r="H61" s="3">
-        <v>10011</v>
-      </c>
-      <c r="I61" s="12" t="s">
+      <c r="F61" s="3">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J61" s="11" t="s">
-        <v>100</v>
+      <c r="H61" s="9"/>
+      <c r="I61" s="3">
+        <v>10007</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B62" s="3">
-        <v>22004</v>
+        <v>21008</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D62" s="3">
         <v>2</v>
@@ -13558,53 +13830,57 @@
       <c r="E62" s="3">
         <v>1</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62" s="9"/>
-      <c r="H62" s="3">
-        <v>10012</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>103</v>
+      <c r="F62" s="3">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H62" s="9"/>
+      <c r="I62" s="3">
+        <v>10008</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B63" s="3">
-        <v>22005</v>
+        <v>22001</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D63" s="3">
         <v>2</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="F63" s="3">
+        <v>2</v>
       </c>
       <c r="G63" s="9"/>
-      <c r="H63" s="3">
-        <v>10013</v>
-      </c>
-      <c r="I63" s="12" t="s">
-        <v>105</v>
+      <c r="H63" s="9"/>
+      <c r="I63" s="3">
+        <v>10009</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>47</v>
+        <v>106</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
+    <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
       <c r="B64" s="3">
-        <v>22006</v>
+        <v>22002</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D64" s="3">
         <v>2</v>
@@ -13612,26 +13888,29 @@
       <c r="E64" s="3">
         <v>1</v>
       </c>
-      <c r="F64" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G64" s="9"/>
-      <c r="H64" s="3">
-        <v>10014</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="J64" s="11" t="s">
+      <c r="F64" s="3">
+        <v>2</v>
+      </c>
+      <c r="G64" s="9" t="s">
         <v>108</v>
       </c>
+      <c r="H64" s="9"/>
+      <c r="I64" s="3">
+        <v>10010</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B65" s="3">
-        <v>22007</v>
+        <v>22003</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D65" s="3">
         <v>2</v>
@@ -13639,26 +13918,29 @@
       <c r="E65" s="3">
         <v>1</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G65" s="9"/>
-      <c r="H65" s="3">
-        <v>10015</v>
-      </c>
-      <c r="I65" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>110</v>
+      <c r="F65" s="3">
+        <v>2</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H65" s="9"/>
+      <c r="I65" s="3">
+        <v>10011</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B66" s="3">
-        <v>22008</v>
+        <v>22004</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D66" s="3">
         <v>2</v>
@@ -13666,53 +13948,59 @@
       <c r="E66" s="3">
         <v>1</v>
       </c>
-      <c r="F66" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G66" s="9"/>
-      <c r="H66" s="3">
-        <v>10016</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>112</v>
+      <c r="F66" s="3">
+        <v>2</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H66" s="9"/>
+      <c r="I66" s="3">
+        <v>10012</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B67" s="3">
-        <v>23001</v>
+        <v>22005</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D67" s="3">
         <v>2</v>
       </c>
       <c r="E67" s="3">
-        <v>1</v>
-      </c>
-      <c r="F67" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="F67" s="3">
+        <v>2</v>
+      </c>
       <c r="G67" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H67" s="3">
-        <v>10017</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>35</v>
+        <v>116</v>
+      </c>
+      <c r="H67" s="9"/>
+      <c r="I67" s="3">
+        <v>10013</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B68" s="3">
-        <v>23002</v>
+        <v>22006</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D68" s="3">
         <v>2</v>
@@ -13720,26 +14008,29 @@
       <c r="E68" s="3">
         <v>1</v>
       </c>
-      <c r="F68" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" s="9"/>
-      <c r="H68" s="3">
-        <v>10018</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>116</v>
+      <c r="F68" s="3">
+        <v>2</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H68" s="9"/>
+      <c r="I68" s="3">
+        <v>10014</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B69" s="3">
-        <v>23003</v>
+        <v>22007</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -13747,26 +14038,29 @@
       <c r="E69" s="3">
         <v>1</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G69" s="9"/>
-      <c r="H69" s="3">
-        <v>10019</v>
-      </c>
-      <c r="I69" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J69" s="11" t="s">
+      <c r="F69" s="3">
+        <v>2</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>118</v>
       </c>
+      <c r="H69" s="9"/>
+      <c r="I69" s="3">
+        <v>10015</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B70" s="3">
-        <v>23004</v>
+        <v>22008</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D70" s="3">
         <v>2</v>
@@ -13774,53 +14068,59 @@
       <c r="E70" s="3">
         <v>1</v>
       </c>
-      <c r="F70" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G70" s="9"/>
-      <c r="H70" s="3">
-        <v>10020</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>121</v>
+      <c r="F70" s="3">
+        <v>2</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H70" s="9"/>
+      <c r="I70" s="3">
+        <v>10016</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B71" s="3">
-        <v>23005</v>
+        <v>23001</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D71" s="3">
         <v>2</v>
       </c>
       <c r="E71" s="3">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3">
         <v>3</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="G71" s="9"/>
-      <c r="H71" s="3">
-        <v>10021</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>124</v>
+      <c r="H71" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I71" s="3">
+        <v>10017</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B72" s="3">
-        <v>23006</v>
+        <v>23002</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -13828,24 +14128,29 @@
       <c r="E72" s="3">
         <v>1</v>
       </c>
-      <c r="F72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G72" s="9"/>
-      <c r="H72" s="3">
-        <v>10001</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J72" s="11"/>
+      <c r="F72" s="3">
+        <v>3</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H72" s="9"/>
+      <c r="I72" s="3">
+        <v>10018</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B73" s="3">
-        <v>23007</v>
+        <v>23003</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D73" s="3">
         <v>2</v>
@@ -13853,24 +14158,29 @@
       <c r="E73" s="3">
         <v>1</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G73" s="9"/>
-      <c r="H73" s="3">
-        <v>10002</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J73" s="11"/>
+      <c r="F73" s="3">
+        <v>3</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H73" s="9"/>
+      <c r="I73" s="3">
+        <v>10019</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>130</v>
+      </c>
     </row>
-    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B74" s="3">
-        <v>23008</v>
+        <v>23004</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
@@ -13878,49 +14188,59 @@
       <c r="E74" s="3">
         <v>1</v>
       </c>
-      <c r="F74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="3">
-        <v>10003</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J74" s="11"/>
+      <c r="F74" s="3">
+        <v>3</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H74" s="9"/>
+      <c r="I74" s="3">
+        <v>10020</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>133</v>
+      </c>
     </row>
-    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B75" s="3">
-        <v>24001</v>
+        <v>23005</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
       </c>
       <c r="E75" s="3">
-        <v>1</v>
-      </c>
-      <c r="F75" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="F75" s="3">
+        <v>3</v>
+      </c>
       <c r="G75" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H75" s="3">
-        <v>10004</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J75" s="11"/>
+        <v>134</v>
+      </c>
+      <c r="H75" s="9"/>
+      <c r="I75" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B76" s="3">
-        <v>24002</v>
+        <v>23006</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D76" s="3">
         <v>2</v>
@@ -13928,24 +14248,27 @@
       <c r="E76" s="3">
         <v>1</v>
       </c>
-      <c r="F76" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G76" s="9"/>
-      <c r="H76" s="3">
-        <v>10005</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J76" s="11"/>
+      <c r="F76" s="3">
+        <v>3</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H76" s="9"/>
+      <c r="I76" s="3">
+        <v>10001</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K76" s="11"/>
     </row>
-    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="77" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B77" s="3">
-        <v>24003</v>
+        <v>23007</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D77" s="3">
         <v>2</v>
@@ -13953,24 +14276,27 @@
       <c r="E77" s="3">
         <v>1</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G77" s="9"/>
-      <c r="H77" s="3">
-        <v>10006</v>
-      </c>
-      <c r="I77" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="J77" s="11"/>
+      <c r="F77" s="3">
+        <v>3</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H77" s="9"/>
+      <c r="I77" s="3">
+        <v>10002</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="K77" s="11"/>
     </row>
-    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B78" s="3">
-        <v>24004</v>
+        <v>23008</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D78" s="3">
         <v>2</v>
@@ -13978,49 +14304,55 @@
       <c r="E78" s="3">
         <v>1</v>
       </c>
-      <c r="F78" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G78" s="9"/>
-      <c r="H78" s="3">
-        <v>10007</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="J78" s="11"/>
+      <c r="F78" s="3">
+        <v>3</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H78" s="9"/>
+      <c r="I78" s="3">
+        <v>10003</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="K78" s="11"/>
     </row>
-    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="79" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B79" s="3">
-        <v>24005</v>
+        <v>24001</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
       </c>
       <c r="E79" s="3">
-        <v>3</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="F79" s="3">
+        <v>4</v>
       </c>
       <c r="G79" s="9"/>
-      <c r="H79" s="3">
-        <v>10008</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J79" s="11"/>
+      <c r="H79" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" s="3">
+        <v>10004</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K79" s="11"/>
     </row>
-    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="80" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B80" s="3">
-        <v>24006</v>
+        <v>24002</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -14028,24 +14360,27 @@
       <c r="E80" s="3">
         <v>1</v>
       </c>
-      <c r="F80" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G80" s="9"/>
-      <c r="H80" s="3">
-        <v>10009</v>
-      </c>
-      <c r="I80" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J80" s="11"/>
+      <c r="F80" s="3">
+        <v>4</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H80" s="9"/>
+      <c r="I80" s="3">
+        <v>10005</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="K80" s="11"/>
     </row>
-    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="81" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B81" s="3">
-        <v>24007</v>
+        <v>24003</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -14053,24 +14388,27 @@
       <c r="E81" s="3">
         <v>1</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G81" s="9"/>
-      <c r="H81" s="3">
-        <v>10010</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="J81" s="11"/>
+      <c r="F81" s="3">
+        <v>4</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H81" s="9"/>
+      <c r="I81" s="3">
+        <v>10006</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="K81" s="11"/>
     </row>
-    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="82" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B82" s="3">
-        <v>24008</v>
+        <v>24004</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D82" s="3">
         <v>2</v>
@@ -14078,49 +14416,55 @@
       <c r="E82" s="3">
         <v>1</v>
       </c>
-      <c r="F82" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G82" s="9"/>
-      <c r="H82" s="3">
-        <v>10011</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J82" s="11"/>
+      <c r="F82" s="3">
+        <v>4</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H82" s="9"/>
+      <c r="I82" s="3">
+        <v>10007</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K82" s="11"/>
     </row>
-    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="83" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B83" s="3">
-        <v>25001</v>
+        <v>24005</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D83" s="3">
         <v>2</v>
       </c>
       <c r="E83" s="3">
-        <v>1</v>
-      </c>
-      <c r="F83" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
+        <v>4</v>
+      </c>
       <c r="G83" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H83" s="3">
-        <v>10012</v>
-      </c>
-      <c r="I83" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J83" s="11"/>
+        <v>141</v>
+      </c>
+      <c r="H83" s="9"/>
+      <c r="I83" s="3">
+        <v>10008</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K83" s="11"/>
     </row>
-    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="84" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B84" s="3">
-        <v>25002</v>
+        <v>24006</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D84" s="3">
         <v>2</v>
@@ -14128,24 +14472,27 @@
       <c r="E84" s="3">
         <v>1</v>
       </c>
-      <c r="F84" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G84" s="9"/>
-      <c r="H84" s="3">
-        <v>10013</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J84" s="11"/>
+      <c r="F84" s="3">
+        <v>4</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H84" s="9"/>
+      <c r="I84" s="3">
+        <v>10009</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K84" s="11"/>
     </row>
-    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="85" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B85" s="3">
-        <v>25003</v>
+        <v>24007</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D85" s="3">
         <v>2</v>
@@ -14153,24 +14500,27 @@
       <c r="E85" s="3">
         <v>1</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G85" s="9"/>
-      <c r="H85" s="3">
-        <v>10014</v>
-      </c>
-      <c r="I85" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J85" s="11"/>
+      <c r="F85" s="3">
+        <v>4</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H85" s="9"/>
+      <c r="I85" s="3">
+        <v>10010</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K85" s="11"/>
     </row>
-    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="86" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B86" s="3">
-        <v>25004</v>
+        <v>24008</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D86" s="3">
         <v>2</v>
@@ -14178,49 +14528,55 @@
       <c r="E86" s="3">
         <v>1</v>
       </c>
-      <c r="F86" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G86" s="9"/>
-      <c r="H86" s="3">
-        <v>10015</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="J86" s="11"/>
+      <c r="F86" s="3">
+        <v>4</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H86" s="9"/>
+      <c r="I86" s="3">
+        <v>10011</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K86" s="11"/>
     </row>
-    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="87" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B87" s="3">
-        <v>25005</v>
+        <v>25001</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
       </c>
       <c r="E87" s="3">
-        <v>3</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F87" s="3">
+        <v>5</v>
       </c>
       <c r="G87" s="9"/>
-      <c r="H87" s="3">
-        <v>10016</v>
-      </c>
-      <c r="I87" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J87" s="11"/>
+      <c r="H87" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I87" s="3">
+        <v>10012</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K87" s="11"/>
     </row>
-    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="88" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B88" s="3">
-        <v>25006</v>
+        <v>25002</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -14228,24 +14584,27 @@
       <c r="E88" s="3">
         <v>1</v>
       </c>
-      <c r="F88" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G88" s="9"/>
-      <c r="H88" s="3">
-        <v>10017</v>
-      </c>
-      <c r="I88" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="J88" s="11"/>
+      <c r="F88" s="3">
+        <v>5</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H88" s="9"/>
+      <c r="I88" s="3">
+        <v>10013</v>
+      </c>
+      <c r="J88" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="K88" s="11"/>
     </row>
-    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="89" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B89" s="3">
-        <v>25007</v>
+        <v>25003</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D89" s="3">
         <v>2</v>
@@ -14253,24 +14612,27 @@
       <c r="E89" s="3">
         <v>1</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G89" s="9"/>
-      <c r="H89" s="3">
-        <v>10018</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="J89" s="11"/>
+      <c r="F89" s="3">
+        <v>5</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H89" s="9"/>
+      <c r="I89" s="3">
+        <v>10014</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K89" s="11"/>
     </row>
-    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="90" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B90" s="3">
-        <v>25008</v>
+        <v>25004</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D90" s="3">
         <v>2</v>
@@ -14278,49 +14640,55 @@
       <c r="E90" s="3">
         <v>1</v>
       </c>
-      <c r="F90" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G90" s="9"/>
-      <c r="H90" s="3">
-        <v>10019</v>
-      </c>
-      <c r="I90" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J90" s="11"/>
+      <c r="F90" s="3">
+        <v>5</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H90" s="9"/>
+      <c r="I90" s="3">
+        <v>10015</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K90" s="11"/>
     </row>
-    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="91" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B91" s="3">
-        <v>26001</v>
+        <v>25005</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D91" s="3">
         <v>2</v>
       </c>
       <c r="E91" s="3">
-        <v>1</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G91" s="9"/>
-      <c r="H91" s="3">
-        <v>10020</v>
-      </c>
-      <c r="I91" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="J91" s="11"/>
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>5</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H91" s="9"/>
+      <c r="I91" s="3">
+        <v>10016</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K91" s="11"/>
     </row>
-    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:10">
+    <row r="92" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B92" s="3">
-        <v>26002</v>
+        <v>25006</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D92" s="3">
         <v>2</v>
@@ -14328,24 +14696,27 @@
       <c r="E92" s="3">
         <v>1</v>
       </c>
-      <c r="F92" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="G92" s="9"/>
-      <c r="H92" s="3">
-        <v>10021</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J92" s="11"/>
+      <c r="F92" s="3">
+        <v>5</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H92" s="9"/>
+      <c r="I92" s="3">
+        <v>10017</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="K92" s="11"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B93" s="3">
-        <v>26003</v>
+        <v>25007</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -14353,20 +14724,27 @@
       <c r="E93" s="3">
         <v>1</v>
       </c>
-      <c r="F93" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G93" s="9"/>
-      <c r="H93" s="3">
-        <v>10021</v>
-      </c>
+      <c r="F93" s="3">
+        <v>5</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H93" s="9"/>
+      <c r="I93" s="3">
+        <v>10018</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="K93" s="11"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B94" s="3">
-        <v>26004</v>
+        <v>25008</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D94" s="3">
         <v>2</v>
@@ -14374,20 +14752,27 @@
       <c r="E94" s="3">
         <v>1</v>
       </c>
-      <c r="F94" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G94" s="9"/>
-      <c r="H94" s="3">
-        <v>10021</v>
-      </c>
+      <c r="F94" s="3">
+        <v>5</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H94" s="9"/>
+      <c r="I94" s="3">
+        <v>10019</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K94" s="11"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
       <c r="B95" s="3">
-        <v>26005</v>
+        <v>26001</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D95" s="3">
         <v>2</v>
@@ -14395,13 +14780,185 @@
       <c r="E95" s="3">
         <v>1</v>
       </c>
-      <c r="F95" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G95" s="9"/>
-      <c r="H95" s="3">
+      <c r="F95" s="3"/>
+      <c r="G95" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="H95" s="9"/>
+      <c r="I95" s="3">
+        <v>10020</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="K95" s="11"/>
+    </row>
+    <row r="96" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B96" s="3">
+        <v>26002</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" s="3">
+        <v>2</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H96" s="9"/>
+      <c r="I96" s="3">
         <v>10021</v>
       </c>
+      <c r="J96" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="K96" s="11"/>
+    </row>
+    <row r="97" ht="19" customHeight="1" spans="2:11">
+      <c r="B97" s="3">
+        <v>26003</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" s="3">
+        <v>2</v>
+      </c>
+      <c r="E97" s="3">
+        <v>1</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H97" s="9"/>
+      <c r="I97" s="3">
+        <v>10021</v>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1" spans="2:11">
+      <c r="B98" s="3">
+        <v>26004</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" s="3">
+        <v>2</v>
+      </c>
+      <c r="E98" s="3">
+        <v>1</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H98" s="9"/>
+      <c r="I98" s="3">
+        <v>10021</v>
+      </c>
+    </row>
+    <row r="99" ht="21" customHeight="1" spans="2:11">
+      <c r="B99" s="3">
+        <v>26005</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" s="3">
+        <v>2</v>
+      </c>
+      <c r="E99" s="3">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H99" s="9"/>
+      <c r="I99" s="3">
+        <v>10021</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B100" s="3">
+        <v>27001</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D100" s="3">
+        <v>2</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1</v>
+      </c>
+      <c r="F100" s="3">
+        <v>6</v>
+      </c>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
+      <c r="I100" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J100" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K100" s="11"/>
+    </row>
+    <row r="101" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B101" s="3">
+        <v>27002</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D101" s="3">
+        <v>2</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1</v>
+      </c>
+      <c r="F101" s="3">
+        <v>7</v>
+      </c>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
+      <c r="I101" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K101" s="11"/>
+    </row>
+    <row r="102" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B102" s="3">
+        <v>27003</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D102" s="3">
+        <v>2</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3">
+        <v>8</v>
+      </c>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
+      <c r="I102" s="3">
+        <v>10021</v>
+      </c>
+      <c r="J102" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K102" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/LongYinConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LongYinConfig.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="166">
   <si>
     <t>##var</t>
   </si>
@@ -164,289 +164,319 @@
     <t>310160</t>
   </si>
   <si>
+    <t>攻击永久提升1%。</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;100402;0.01</t>
+  </si>
+  <si>
+    <t>魔焰地裂会对目标释放爆裂状态,3秒后对范围内造成200%爆炸伤害。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100010</t>
+  </si>
+  <si>
+    <t>前冲距离延长2码/。</t>
+  </si>
+  <si>
+    <t>11002,11003</t>
+  </si>
+  <si>
+    <t>魔焰地裂会使目标受到伤害提升10%,持续5秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100011</t>
+  </si>
+  <si>
+    <t>11004</t>
+  </si>
+  <si>
+    <t>幻影跃击伤害提升30%/60%/100%。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;2;0.3#SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;2;0.6#SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;2;1</t>
+  </si>
+  <si>
+    <t>11005</t>
+  </si>
+  <si>
+    <t>魔焰地裂使目标移动速度降低30%，持续3秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100012</t>
+  </si>
+  <si>
+    <t>释放旋舞之影使自身的移动速度提升50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;6;11100010</t>
+  </si>
+  <si>
+    <t>技能攻击怪物伤害提升2%。</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;223103;0.02</t>
+  </si>
+  <si>
+    <t>310161</t>
+  </si>
+  <si>
     <t>描述。。。。</t>
   </si>
   <si>
+    <t>SkillIdAdd;1301002</t>
+  </si>
+  <si>
+    <t>12001</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;200303;0.01#RolePropertyAdd;200303;0.02#RolePropertyAdd;200303;0.03#RolePropertyAdd;200303;0.04#RolePropertyAdd;200303;0.05</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;1301003</t>
+  </si>
+  <si>
+    <t>12002,12003</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.08#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.16#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.24#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.32#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.4</t>
+  </si>
+  <si>
+    <t>12004</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;1301006#SkillIdAdd;1301007#SkillIdAdd;1301008#SkillIdAdd;1301009#SkillIdAdd;1301010</t>
+  </si>
+  <si>
+    <t>12005</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;4;2</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;200103;0.01#RolePropertyAdd;200103;0.02#RolePropertyAdd;200103;0.03#RolePropertyAdd;200103;0.04#RolePropertyAdd;200103;0.05</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;205603;0.1</t>
+  </si>
+  <si>
+    <t>310162</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;203603;0.01#RolePropertyAdd;203603;0.02#RolePropertyAdd;203603;0.03#RolePropertyAdd;203603;0.04#RolePropertyAdd;203603;0.05</t>
+  </si>
+  <si>
+    <t>13001</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;4;2</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.2#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.4#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.6#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.8#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;1</t>
+  </si>
+  <si>
+    <t>13002,13003</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;204003;0.1</t>
+  </si>
+  <si>
+    <t>13004</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1200001,1200002,1200003;2;0.08#SkillPropertyAdd;1200001,1200002,1200003;2;0.16#SkillPropertyAdd;1200001,1200002,1200003;2;0.24#SkillPropertyAdd;1200001,1200002,1200003;2;0.32#SkillPropertyAdd;1200001,1200002,1200003;2;0.4</t>
+  </si>
+  <si>
+    <t>13005</t>
+  </si>
+  <si>
+    <t>310163</t>
+  </si>
+  <si>
+    <t>14001</t>
+  </si>
+  <si>
+    <t>14002,14003</t>
+  </si>
+  <si>
+    <t>14004</t>
+  </si>
+  <si>
+    <t>14005</t>
+  </si>
+  <si>
+    <t>310164</t>
+  </si>
+  <si>
+    <t>15001</t>
+  </si>
+  <si>
+    <t>15002,15003</t>
+  </si>
+  <si>
+    <t>15004</t>
+  </si>
+  <si>
+    <t>15005</t>
+  </si>
+  <si>
+    <t>11004,12004</t>
+  </si>
+  <si>
+    <t>12004,13004</t>
+  </si>
+  <si>
+    <t>13004,14004</t>
+  </si>
+  <si>
+    <t>14004,15004</t>
+  </si>
+  <si>
+    <t>15004,11004</t>
+  </si>
+  <si>
+    <t>双龙觉醒</t>
+  </si>
+  <si>
+    <t>双龙觉醒很牛逼</t>
+  </si>
+  <si>
+    <t>三龙觉醒</t>
+  </si>
+  <si>
+    <t>三龙觉醒很牛逼</t>
+  </si>
+  <si>
+    <t>五龙觉醒</t>
+  </si>
+  <si>
+    <t>五龙觉醒很牛逼</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>攻击永久提升1%/2%/3%。</t>
+  </si>
+  <si>
     <t>RolePropertyAdd;100402;0.01#RolePropertyAdd;100402;0.02#RolePropertyAdd;100402;0.03</t>
   </si>
   <si>
-    <t>SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100010</t>
-  </si>
-  <si>
-    <t>11002,11003</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100011</t>
-  </si>
-  <si>
-    <t>11004</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;2;0.3#SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;2;0.6#SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;2;1</t>
-  </si>
-  <si>
-    <t>11005</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100012#SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100013#SkillPropertyAdd;1110002,1110003,1110004,1110005,1110006;6;11100014</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;6;11100010</t>
+    <t>21001</t>
+  </si>
+  <si>
+    <t>冰封冲击技能冷却时间缩减2秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;4;2</t>
+  </si>
+  <si>
+    <t>冰封冲击伤害提升30%/60%/100%。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;2;0.3#SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;2;0.6#SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;2;1</t>
+  </si>
+  <si>
+    <t>21002,21003</t>
+  </si>
+  <si>
+    <t>普攻使目标移动速度降低30%,持续3秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1200101,1200102;6;1000001</t>
+  </si>
+  <si>
+    <t>21004</t>
+  </si>
+  <si>
+    <t>破冰飞弹伤害提升30%,60%,100%。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;2;0.3#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;2;0.6#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;2;1</t>
+  </si>
+  <si>
+    <t>21005</t>
+  </si>
+  <si>
+    <t>破冰飞弹使目标受到伤害增加10%/20%/30%。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;6;11200110#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;6;11200111#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;6;11200112</t>
+  </si>
+  <si>
+    <t>每次暴击有30%概率对目标附加伤害加深状态,使其受到伤害增加25%,持续3秒。</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;1302001</t>
+  </si>
+  <si>
+    <t>重击概率提升1%/2%/3%/4%/5%。</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;202103;0.01#RolePropertyAdd;202103;0.02#RolePropertyAdd;202103;0.03#RolePropertyAdd;202103;0.04#RolePropertyAdd;202103;0.05</t>
+  </si>
+  <si>
+    <t>普通攻击有10%概率触发破冰飞弹。</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;1302003</t>
+  </si>
+  <si>
+    <t>22001</t>
+  </si>
+  <si>
+    <t>普通伤害提升3%/6%/9%/12%/15%。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1200101,1200102;2;0.03#SkillPropertyAdd;1200101,1200102;2;0.06#SkillPropertyAdd;1200101,1200102;2;0.09#SkillPropertyAdd;1200101,1200102;2;0.12#SkillPropertyAdd;1200101,1200102;2;0.15</t>
+  </si>
+  <si>
+    <t>攻击目标有10%概率提升自身25%伤害,持续3秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1200101,1200102;6;12001010</t>
+  </si>
+  <si>
+    <t>22002,22003</t>
+  </si>
+  <si>
+    <t>圣御之击伤害提升20%/40%/60%/80%100%。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.2#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.4#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.6#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.8#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;1</t>
+  </si>
+  <si>
+    <t>22004</t>
+  </si>
+  <si>
+    <t>暴击上限永久提升1%/2%/3%/4%/5%。</t>
+  </si>
+  <si>
+    <t>22005</t>
+  </si>
+  <si>
+    <t>圣御之击冷却时间降低1秒。</t>
+  </si>
+  <si>
+    <t>SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;4;1</t>
+  </si>
+  <si>
+    <t>技能有1%/2%/3%/4%/5%概率造成双倍伤害。</t>
+  </si>
+  <si>
+    <t>RolePropertyAdd;204103;0.01#RolePropertyAdd;204103;0.02#RolePropertyAdd;204103;0.03#RolePropertyAdd;204103;0.04#RolePropertyAdd;204103;0.05</t>
+  </si>
+  <si>
+    <t>受到攻击有10%概率对目标释放圣御之击。</t>
+  </si>
+  <si>
+    <t>SkillIdAdd;1302004</t>
+  </si>
+  <si>
+    <t>技能攻击怪物伤害提升2%/4%/6%/8%/10%。</t>
   </si>
   <si>
     <t>RolePropertyAdd;223103;0.02#RolePropertyAdd;223103;0.04#RolePropertyAdd;223103;0.06#RolePropertyAdd;223103;0.08#RolePropertyAdd;223103;0.1</t>
-  </si>
-  <si>
-    <t>310161</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;1301002</t>
-  </si>
-  <si>
-    <t>12001</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;200303;0.01#RolePropertyAdd;200303;0.02#RolePropertyAdd;200303;0.03#RolePropertyAdd;200303;0.04#RolePropertyAdd;200303;0.05</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;1301003</t>
-  </si>
-  <si>
-    <t>12002,12003</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.08#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.16#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.24#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.32#SkillPropertyAdd;1110022,1110023,1110024,1110025,1110026;2;0.4</t>
-  </si>
-  <si>
-    <t>12004</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;1301006#SkillIdAdd;1301007#SkillIdAdd;1301008#SkillIdAdd;1301009#SkillIdAdd;1301010</t>
-  </si>
-  <si>
-    <t>12005</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;4;2</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;200103;0.01#RolePropertyAdd;200103;0.02#RolePropertyAdd;200103;0.03#RolePropertyAdd;200103;0.04#RolePropertyAdd;200103;0.05</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;205603;0.1</t>
-  </si>
-  <si>
-    <t>310162</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;203603;0.01#RolePropertyAdd;203603;0.02#RolePropertyAdd;203603;0.03#RolePropertyAdd;203603;0.04#RolePropertyAdd;203603;0.05</t>
-  </si>
-  <si>
-    <t>13001</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110012,1110013,1110014,1110015,1110016;4;2</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.2#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.4#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.6#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;0.8#SkillPropertyAdd;1110032,1110033,1110034,1110035,1110036;2;1</t>
-  </si>
-  <si>
-    <t>13002,13003</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;204003;0.1</t>
-  </si>
-  <si>
-    <t>13004</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1200001,1200002,1200003;2;0.08#SkillPropertyAdd;1200001,1200002,1200003;2;0.16#SkillPropertyAdd;1200001,1200002,1200003;2;0.24#SkillPropertyAdd;1200001,1200002,1200003;2;0.32#SkillPropertyAdd;1200001,1200002,1200003;2;0.4</t>
-  </si>
-  <si>
-    <t>13005</t>
-  </si>
-  <si>
-    <t>310163</t>
-  </si>
-  <si>
-    <t>14001</t>
-  </si>
-  <si>
-    <t>14002,14003</t>
-  </si>
-  <si>
-    <t>14004</t>
-  </si>
-  <si>
-    <t>14005</t>
-  </si>
-  <si>
-    <t>310164</t>
-  </si>
-  <si>
-    <t>15001</t>
-  </si>
-  <si>
-    <t>15002,15003</t>
-  </si>
-  <si>
-    <t>15004</t>
-  </si>
-  <si>
-    <t>15005</t>
-  </si>
-  <si>
-    <t>11004,12004</t>
-  </si>
-  <si>
-    <t>12004,13004</t>
-  </si>
-  <si>
-    <t>13004,14004</t>
-  </si>
-  <si>
-    <t>14004,15004</t>
-  </si>
-  <si>
-    <t>15004,11004</t>
-  </si>
-  <si>
-    <t>双龙觉醒</t>
-  </si>
-  <si>
-    <t>双龙觉醒很牛逼</t>
-  </si>
-  <si>
-    <t>三龙觉醒</t>
-  </si>
-  <si>
-    <t>三龙觉醒很牛逼</t>
-  </si>
-  <si>
-    <t>五龙觉醒</t>
-  </si>
-  <si>
-    <t>五龙觉醒很牛逼</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>攻击永久提升1%/2%/3%。</t>
-  </si>
-  <si>
-    <t>21001</t>
-  </si>
-  <si>
-    <t>冰封冲击技能冷却时间缩减2秒。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;4;2</t>
-  </si>
-  <si>
-    <t>冰封冲击伤害提升30%/60%/100%。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;2;0.3#SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;2;0.6#SkillPropertyAdd;1120002,1120003,1120004,1120005,1120006;2;1</t>
-  </si>
-  <si>
-    <t>21002,21003</t>
-  </si>
-  <si>
-    <t>普攻使目标移动速度降低30%,持续3秒。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1200101,1200102;6;1000001</t>
-  </si>
-  <si>
-    <t>21004</t>
-  </si>
-  <si>
-    <t>破冰飞弹伤害提升30%,60%,100%。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;2;0.3#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;2;0.6#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;2;1</t>
-  </si>
-  <si>
-    <t>21005</t>
-  </si>
-  <si>
-    <t>破冰飞弹使目标受到伤害增加10%/20%/30%。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;6;11200110#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;6;11200111#SkillPropertyAdd;1120012,1120013,1120014,1120015,1120016;6;11200112</t>
-  </si>
-  <si>
-    <t>每次暴击有30%概率对目标附加伤害加深状态,使其受到伤害增加25%,持续3秒。</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;1302001</t>
-  </si>
-  <si>
-    <t>重击概率提升1%/2%/3%/4%/5%。</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;202103;0.01#RolePropertyAdd;202103;0.02#RolePropertyAdd;202103;0.03#RolePropertyAdd;202103;0.04#RolePropertyAdd;202103;0.05</t>
-  </si>
-  <si>
-    <t>普通攻击有10%概率触发破冰飞弹。</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;1302003</t>
-  </si>
-  <si>
-    <t>22001</t>
-  </si>
-  <si>
-    <t>普通伤害提升3%/6%/9%/12%/15%。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1200101,1200102;2;0.03#SkillPropertyAdd;1200101,1200102;2;0.06#SkillPropertyAdd;1200101,1200102;2;0.09#SkillPropertyAdd;1200101,1200102;2;0.12#SkillPropertyAdd;1200101,1200102;2;0.15</t>
-  </si>
-  <si>
-    <t>攻击目标有10%概率提升自身25%伤害,持续3秒。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1200101,1200102;6;12001010</t>
-  </si>
-  <si>
-    <t>22002,22003</t>
-  </si>
-  <si>
-    <t>圣御之击伤害提升20%/40%/60%/80%100%。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.2#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.4#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.6#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;0.8#SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;2;1</t>
-  </si>
-  <si>
-    <t>22004</t>
-  </si>
-  <si>
-    <t>暴击上限永久提升1%/2%/3%/4%/5%。</t>
-  </si>
-  <si>
-    <t>22005</t>
-  </si>
-  <si>
-    <t>圣御之击冷却时间降低1秒。</t>
-  </si>
-  <si>
-    <t>SkillPropertyAdd;1120022,1120023,1120024,1120025,1120026;4;1</t>
-  </si>
-  <si>
-    <t>技能有1%/2%/3%/4%/5%概率造成双倍伤害。</t>
-  </si>
-  <si>
-    <t>RolePropertyAdd;204103;0.01#RolePropertyAdd;204103;0.02#RolePropertyAdd;204103;0.03#RolePropertyAdd;204103;0.04#RolePropertyAdd;204103;0.05</t>
-  </si>
-  <si>
-    <t>受到攻击有10%概率对目标释放圣御之击。</t>
-  </si>
-  <si>
-    <t>SkillIdAdd;1302004</t>
-  </si>
-  <si>
-    <t>技能攻击怪物伤害提升2%/4%/6%/8%/10%。</t>
   </si>
   <si>
     <t>23001</t>
@@ -11766,7 +11796,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{5A70E253-88C2-49D2-983F-EC4F1DC39A57}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{B68D6529-0FD2-44B7-BAE6-47974271CC18}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -12276,10 +12306,10 @@
         <v>10002</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12306,7 +12336,7 @@
         <v>10003</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K8" s="11"/>
     </row>
@@ -12327,17 +12357,17 @@
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="3">
         <v>10004</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12357,17 +12387,17 @@
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="3">
         <v>10005</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12387,17 +12417,17 @@
         <v>1</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="3">
         <v>10006</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12417,17 +12447,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="3">
         <v>10007</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12447,17 +12477,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="3">
         <v>10008</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12478,16 +12508,16 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I14" s="3">
         <v>10009</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12507,17 +12537,17 @@
         <v>2</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="3">
         <v>10010</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -12537,17 +12567,17 @@
         <v>2</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="3">
         <v>10011</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12567,17 +12597,17 @@
         <v>2</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="3">
         <v>10012</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12597,17 +12627,17 @@
         <v>2</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="3">
         <v>10013</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12627,17 +12657,17 @@
         <v>2</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="3">
         <v>10014</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12657,17 +12687,17 @@
         <v>2</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="3">
         <v>10015</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12687,17 +12717,17 @@
         <v>2</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="3">
         <v>10016</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12718,16 +12748,16 @@
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I22" s="3">
         <v>10017</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12747,17 +12777,17 @@
         <v>3</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="3">
         <v>10018</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12777,17 +12807,17 @@
         <v>3</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="3">
         <v>10019</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12807,17 +12837,17 @@
         <v>3</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="3">
         <v>10020</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12837,17 +12867,17 @@
         <v>3</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="3">
         <v>10021</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -12867,14 +12897,14 @@
         <v>3</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="3">
         <v>10001</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K27" s="11"/>
     </row>
@@ -12895,14 +12925,14 @@
         <v>3</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="3">
         <v>10002</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K28" s="11"/>
     </row>
@@ -12923,14 +12953,14 @@
         <v>3</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="3">
         <v>10003</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K29" s="11"/>
     </row>
@@ -12952,13 +12982,13 @@
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="I30" s="3">
         <v>10004</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K30" s="11"/>
     </row>
@@ -12979,14 +13009,14 @@
         <v>4</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="3">
         <v>10005</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K31" s="11"/>
     </row>
@@ -13007,14 +13037,14 @@
         <v>4</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="3">
         <v>10006</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -13035,14 +13065,14 @@
         <v>4</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="3">
         <v>10007</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K33" s="11"/>
     </row>
@@ -13063,14 +13093,14 @@
         <v>4</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H34" s="9"/>
       <c r="I34" s="3">
         <v>10008</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K34" s="11"/>
     </row>
@@ -13091,14 +13121,14 @@
         <v>4</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="3">
         <v>10009</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K35" s="11"/>
     </row>
@@ -13119,14 +13149,14 @@
         <v>4</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H36" s="9"/>
       <c r="I36" s="3">
         <v>10010</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -13147,14 +13177,14 @@
         <v>4</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="3">
         <v>10011</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -13176,13 +13206,13 @@
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I38" s="3">
         <v>10012</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -13203,14 +13233,14 @@
         <v>5</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="3">
         <v>10013</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -13231,14 +13261,14 @@
         <v>5</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="3">
         <v>10014</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -13259,14 +13289,14 @@
         <v>5</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="3">
         <v>10015</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K41" s="11"/>
     </row>
@@ -13287,14 +13317,14 @@
         <v>5</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="3">
         <v>10016</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -13315,14 +13345,14 @@
         <v>5</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="3">
         <v>10017</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K43" s="11"/>
     </row>
@@ -13343,14 +13373,14 @@
         <v>5</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="3">
         <v>10018</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K44" s="11"/>
     </row>
@@ -13371,14 +13401,14 @@
         <v>5</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="3">
         <v>10019</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K45" s="11"/>
     </row>
@@ -13397,14 +13427,14 @@
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="9" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="3">
         <v>10020</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K46" s="11"/>
     </row>
@@ -13423,14 +13453,14 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="9" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="3">
         <v>10021</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K47" s="11"/>
     </row>
@@ -13449,14 +13479,14 @@
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="3">
         <v>10021</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K48" s="11"/>
     </row>
@@ -13475,14 +13505,14 @@
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="3">
         <v>10021</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K49" s="11"/>
     </row>
@@ -13501,14 +13531,14 @@
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="3">
         <v>10021</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K50" s="11"/>
     </row>
@@ -13517,7 +13547,7 @@
         <v>17001</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -13534,7 +13564,7 @@
         <v>10021</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K51" s="11"/>
     </row>
@@ -13543,7 +13573,7 @@
         <v>17002</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -13560,7 +13590,7 @@
         <v>10021</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K52" s="11"/>
     </row>
@@ -13569,7 +13599,7 @@
         <v>17003</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -13586,7 +13616,7 @@
         <v>10021</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K53" s="11"/>
     </row>
@@ -13595,7 +13625,7 @@
         <v>19</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -13631,10 +13661,10 @@
         <v>10001</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13654,17 +13684,17 @@
         <v>1</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="3">
         <v>10002</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13684,17 +13714,17 @@
         <v>1</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H57" s="9"/>
       <c r="I57" s="3">
         <v>10003</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13714,17 +13744,17 @@
         <v>1</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="3">
         <v>10004</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13744,17 +13774,17 @@
         <v>1</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H59" s="9"/>
       <c r="I59" s="3">
         <v>10005</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13774,17 +13804,17 @@
         <v>1</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H60" s="9"/>
       <c r="I60" s="3">
         <v>10006</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13804,17 +13834,17 @@
         <v>1</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H61" s="9"/>
       <c r="I61" s="3">
         <v>10007</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13834,17 +13864,17 @@
         <v>1</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="3">
         <v>10008</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13869,10 +13899,10 @@
         <v>10009</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
@@ -13892,17 +13922,17 @@
         <v>2</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="3">
         <v>10010</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -13922,17 +13952,17 @@
         <v>2</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="3">
         <v>10011</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -13952,17 +13982,17 @@
         <v>2</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="3">
         <v>10012</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -13982,17 +14012,17 @@
         <v>2</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="3">
         <v>10013</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K67" s="12" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14012,17 +14042,17 @@
         <v>2</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="3">
         <v>10014</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14042,17 +14072,17 @@
         <v>2</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="3">
         <v>10015</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14072,17 +14102,17 @@
         <v>2</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H70" s="9"/>
       <c r="I70" s="3">
         <v>10016</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14103,16 +14133,16 @@
       </c>
       <c r="G71" s="9"/>
       <c r="H71" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I71" s="3">
         <v>10017</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14132,17 +14162,17 @@
         <v>3</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H72" s="9"/>
       <c r="I72" s="3">
         <v>10018</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14162,17 +14192,17 @@
         <v>3</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="3">
         <v>10019</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14192,17 +14222,17 @@
         <v>3</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="3">
         <v>10020</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14222,17 +14252,17 @@
         <v>3</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="3">
         <v>10021</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -14252,14 +14282,14 @@
         <v>3</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="3">
         <v>10001</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K76" s="11"/>
     </row>
@@ -14280,14 +14310,14 @@
         <v>3</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="3">
         <v>10002</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K77" s="11"/>
     </row>
@@ -14308,14 +14338,14 @@
         <v>3</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="3">
         <v>10003</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K78" s="11"/>
     </row>
@@ -14337,13 +14367,13 @@
       </c>
       <c r="G79" s="9"/>
       <c r="H79" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I79" s="3">
         <v>10004</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K79" s="11"/>
     </row>
@@ -14364,14 +14394,14 @@
         <v>4</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="3">
         <v>10005</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K80" s="11"/>
     </row>
@@ -14392,14 +14422,14 @@
         <v>4</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="3">
         <v>10006</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K81" s="11"/>
     </row>
@@ -14420,14 +14450,14 @@
         <v>4</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="3">
         <v>10007</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K82" s="11"/>
     </row>
@@ -14448,14 +14478,14 @@
         <v>4</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="3">
         <v>10008</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K83" s="11"/>
     </row>
@@ -14476,14 +14506,14 @@
         <v>4</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="3">
         <v>10009</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="K84" s="11"/>
     </row>
@@ -14504,14 +14534,14 @@
         <v>4</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="3">
         <v>10010</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K85" s="11"/>
     </row>
@@ -14532,14 +14562,14 @@
         <v>4</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="3">
         <v>10011</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K86" s="11"/>
     </row>
@@ -14561,13 +14591,13 @@
       </c>
       <c r="G87" s="9"/>
       <c r="H87" s="9" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="I87" s="3">
         <v>10012</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K87" s="11"/>
     </row>
@@ -14588,14 +14618,14 @@
         <v>5</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="3">
         <v>10013</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K88" s="11"/>
     </row>
@@ -14616,14 +14646,14 @@
         <v>5</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H89" s="9"/>
       <c r="I89" s="3">
         <v>10014</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K89" s="11"/>
     </row>
@@ -14644,14 +14674,14 @@
         <v>5</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="3">
         <v>10015</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="K90" s="11"/>
     </row>
@@ -14672,14 +14702,14 @@
         <v>5</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H91" s="9"/>
       <c r="I91" s="3">
         <v>10016</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K91" s="11"/>
     </row>
@@ -14700,14 +14730,14 @@
         <v>5</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H92" s="9"/>
       <c r="I92" s="3">
         <v>10017</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K92" s="11"/>
     </row>
@@ -14728,14 +14758,14 @@
         <v>5</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H93" s="9"/>
       <c r="I93" s="3">
         <v>10018</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="K93" s="11"/>
     </row>
@@ -14756,14 +14786,14 @@
         <v>5</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="3">
         <v>10019</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K94" s="11"/>
     </row>
@@ -14782,14 +14812,14 @@
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="9" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H95" s="9"/>
       <c r="I95" s="3">
         <v>10020</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K95" s="11"/>
     </row>
@@ -14808,14 +14838,14 @@
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="9" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H96" s="9"/>
       <c r="I96" s="3">
         <v>10021</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K96" s="11"/>
     </row>
@@ -14833,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H97" s="9"/>
       <c r="I97" s="3">
@@ -14854,7 +14884,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="3">
@@ -14875,7 +14905,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H99" s="9"/>
       <c r="I99" s="3">
@@ -14887,7 +14917,7 @@
         <v>27001</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D100" s="3">
         <v>2</v>
@@ -14904,7 +14934,7 @@
         <v>10021</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K100" s="11"/>
     </row>
@@ -14913,7 +14943,7 @@
         <v>27002</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>2</v>
@@ -14930,7 +14960,7 @@
         <v>10021</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K101" s="11"/>
     </row>
@@ -14939,7 +14969,7 @@
         <v>27003</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D102" s="3">
         <v>2</v>
@@ -14956,7 +14986,7 @@
         <v>10021</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K102" s="11"/>
     </row>
